--- a/sample_data/Tutor_Copy_-_Fall_2026_Acceptance___Placement_Choices_for_LRC.xlsx
+++ b/sample_data/Tutor_Copy_-_Fall_2026_Acceptance___Placement_Choices_for_LRC.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andre\tutor_assignment_app\sample_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\tutor_assignment_app\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D88E67-A052-43F0-8D53-71EA7465115D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A6DE31-6C68-43E3-991F-4B30EC5E290A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Placements (Tutors Please Revie" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2541" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2605" uniqueCount="465">
   <si>
     <t>Tutors: Please review your placement(s) and Accept no later than Sunday Aug 16
 If for some reason your availability has changed, you must email LRC Pro Staff ASAP
@@ -1441,6 +1441,66 @@
   </si>
   <si>
     <t>Kassidy Saffa, Jasmine Torres, Ryan Moses (Tuesday only)</t>
+  </si>
+  <si>
+    <t>Link Group</t>
+  </si>
+  <si>
+    <t>BIOL 201 - A</t>
+  </si>
+  <si>
+    <t>BIOL 302 - A</t>
+  </si>
+  <si>
+    <t>COMP 121 - A</t>
+  </si>
+  <si>
+    <t>COMP 151 - A</t>
+  </si>
+  <si>
+    <t>COMP 162 - A</t>
+  </si>
+  <si>
+    <t>COMP 232 - A</t>
+  </si>
+  <si>
+    <t>COMP 262 - A</t>
+  </si>
+  <si>
+    <t>ESRM 203 - A</t>
+  </si>
+  <si>
+    <t>PSY 300 - A</t>
+  </si>
+  <si>
+    <t>PSY 301 - A</t>
+  </si>
+  <si>
+    <t>PSY 314 - A</t>
+  </si>
+  <si>
+    <t>PSY 300 - B</t>
+  </si>
+  <si>
+    <t>PSY 300 - C</t>
+  </si>
+  <si>
+    <t>PSY 300 - D</t>
+  </si>
+  <si>
+    <t>PSY 301 - B</t>
+  </si>
+  <si>
+    <t>PSY 314 - B</t>
+  </si>
+  <si>
+    <t>PSY 301 - C</t>
+  </si>
+  <si>
+    <t>PSY 314 - C</t>
+  </si>
+  <si>
+    <t>PSY 314 - D</t>
   </si>
 </sst>
 </file>
@@ -6551,7 +6611,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N157"/>
+  <dimension ref="A1:O157"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16.90625" customWidth="1"/>
@@ -6566,6 +6626,7 @@
     <col min="10" max="10" width="20.36328125" customWidth="1"/>
     <col min="11" max="11" width="18.6328125" customWidth="1"/>
     <col min="13" max="13" width="17.90625" customWidth="1"/>
+    <col min="15" max="15" width="17.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="12.5">
@@ -6918,7 +6979,7 @@
       <c r="M16" s="120"/>
       <c r="N16" s="120"/>
     </row>
-    <row r="17" spans="1:14" ht="12.5">
+    <row r="17" spans="1:15" ht="12.5">
       <c r="A17" s="48"/>
       <c r="B17" s="146"/>
       <c r="C17" s="120"/>
@@ -6934,7 +6995,7 @@
       <c r="M17" s="48"/>
       <c r="N17" s="48"/>
     </row>
-    <row r="18" spans="1:14" ht="15.5">
+    <row r="18" spans="1:15" ht="16" thickBot="1">
       <c r="A18" s="52"/>
       <c r="B18" s="16" t="s">
         <v>39</v>
@@ -6975,8 +7036,11 @@
       <c r="N18" s="18" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" ht="15.5">
+      <c r="O18" s="18" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="16" thickTop="1">
       <c r="A19" s="24" t="s">
         <v>55</v>
       </c>
@@ -7016,7 +7080,7 @@
         <v>2502</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="15.5">
+    <row r="20" spans="1:15" ht="15.5">
       <c r="A20" s="24" t="s">
         <v>55</v>
       </c>
@@ -7054,7 +7118,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="15.5">
+    <row r="21" spans="1:15" ht="15.5">
       <c r="A21" s="24" t="s">
         <v>55</v>
       </c>
@@ -7092,7 +7156,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="15.5">
+    <row r="22" spans="1:15" ht="15.5">
       <c r="A22" s="24" t="s">
         <v>55</v>
       </c>
@@ -7130,7 +7194,7 @@
         <v>2330</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="15.5">
+    <row r="23" spans="1:15" ht="15.5">
       <c r="A23" s="24" t="s">
         <v>55</v>
       </c>
@@ -7170,7 +7234,7 @@
         <v>2582</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="15.5">
+    <row r="24" spans="1:15" ht="15.5">
       <c r="A24" s="24" t="s">
         <v>74</v>
       </c>
@@ -7208,7 +7272,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="15.5">
+    <row r="25" spans="1:15" ht="15.5">
       <c r="A25" s="24" t="s">
         <v>74</v>
       </c>
@@ -7246,7 +7310,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="15.5">
+    <row r="26" spans="1:15" ht="15.5">
       <c r="A26" s="24" t="s">
         <v>55</v>
       </c>
@@ -7283,8 +7347,11 @@
       <c r="N26" s="63">
         <v>1411</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" ht="15.5">
+      <c r="O26" s="63" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="15.5">
       <c r="A27" s="24" t="s">
         <v>55</v>
       </c>
@@ -7321,8 +7388,11 @@
       <c r="N27" s="63">
         <v>134</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" ht="15.5">
+      <c r="O27" s="63" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="15.5">
       <c r="A28" s="24" t="s">
         <v>55</v>
       </c>
@@ -7359,8 +7429,11 @@
       <c r="N28" s="63">
         <v>134</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" ht="15.5">
+      <c r="O28" s="63" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="15.5">
       <c r="A29" s="24" t="s">
         <v>57</v>
       </c>
@@ -7402,7 +7475,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="31">
+    <row r="30" spans="1:15" ht="31">
       <c r="A30" s="24" t="s">
         <v>57</v>
       </c>
@@ -7442,7 +7515,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15.5">
+    <row r="31" spans="1:15" ht="15.5">
       <c r="A31" s="24" t="s">
         <v>74</v>
       </c>
@@ -7480,7 +7553,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="62">
+    <row r="32" spans="1:15" ht="62">
       <c r="A32" s="24" t="s">
         <v>74</v>
       </c>
@@ -7524,7 +7597,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="46.5">
+    <row r="33" spans="1:15" ht="46.5">
       <c r="A33" s="24" t="s">
         <v>74</v>
       </c>
@@ -7566,7 +7639,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="15.5">
+    <row r="34" spans="1:15" ht="15.5">
       <c r="A34" s="24" t="s">
         <v>55</v>
       </c>
@@ -7604,7 +7677,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="15.5">
+    <row r="35" spans="1:15" ht="15.5">
       <c r="A35" s="24" t="s">
         <v>74</v>
       </c>
@@ -7642,7 +7715,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="15.5">
+    <row r="36" spans="1:15" ht="15.5">
       <c r="A36" s="24" t="s">
         <v>74</v>
       </c>
@@ -7680,7 +7753,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="31">
+    <row r="37" spans="1:15" ht="31">
       <c r="A37" s="24" t="s">
         <v>74</v>
       </c>
@@ -7721,8 +7794,11 @@
       <c r="N37" s="63">
         <v>1422</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" ht="15.5">
+      <c r="O37" s="63" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="15.5">
       <c r="A38" s="24" t="s">
         <v>74</v>
       </c>
@@ -7761,8 +7837,11 @@
       <c r="N38" s="63">
         <v>1422</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" ht="15.5">
+      <c r="O38" s="63" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="15.5">
       <c r="A39" s="24" t="s">
         <v>74</v>
       </c>
@@ -7798,7 +7877,7 @@
       </c>
       <c r="N39" s="63"/>
     </row>
-    <row r="40" spans="1:14" ht="15.5">
+    <row r="40" spans="1:15" ht="15.5">
       <c r="A40" s="24" t="s">
         <v>74</v>
       </c>
@@ -7834,7 +7913,7 @@
       </c>
       <c r="N40" s="63"/>
     </row>
-    <row r="41" spans="1:14" ht="15.5">
+    <row r="41" spans="1:15" ht="15.5">
       <c r="A41" s="24" t="s">
         <v>74</v>
       </c>
@@ -7872,7 +7951,7 @@
         <v>2582</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="15.5">
+    <row r="42" spans="1:15" ht="15.5">
       <c r="A42" s="24" t="s">
         <v>74</v>
       </c>
@@ -7914,7 +7993,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="15.5">
+    <row r="43" spans="1:15" ht="15.5">
       <c r="A43" s="24" t="s">
         <v>74</v>
       </c>
@@ -7954,7 +8033,7 @@
         <v>3540</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="15.5">
+    <row r="44" spans="1:15" ht="15.5">
       <c r="A44" s="24" t="s">
         <v>74</v>
       </c>
@@ -7992,7 +8071,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="31">
+    <row r="45" spans="1:15" ht="31">
       <c r="A45" s="24" t="s">
         <v>74</v>
       </c>
@@ -8036,7 +8115,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="31">
+    <row r="46" spans="1:15" ht="31">
       <c r="A46" s="24" t="s">
         <v>74</v>
       </c>
@@ -8078,7 +8157,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="15.5">
+    <row r="47" spans="1:15" ht="15.5">
       <c r="A47" s="24" t="s">
         <v>74</v>
       </c>
@@ -8122,7 +8201,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="31">
+    <row r="48" spans="1:15" ht="31">
       <c r="A48" s="24" t="s">
         <v>74</v>
       </c>
@@ -8162,7 +8241,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="15.5">
+    <row r="49" spans="1:15" ht="15.5">
       <c r="A49" s="24" t="s">
         <v>74</v>
       </c>
@@ -8200,7 +8279,7 @@
         <v>2570</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="31">
+    <row r="50" spans="1:15" ht="31">
       <c r="A50" s="24" t="s">
         <v>74</v>
       </c>
@@ -8244,7 +8323,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="46.5">
+    <row r="51" spans="1:15" ht="46.5">
       <c r="A51" s="24" t="s">
         <v>74</v>
       </c>
@@ -8286,7 +8365,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="15.5">
+    <row r="52" spans="1:15" ht="15.5">
       <c r="A52" s="24" t="s">
         <v>57</v>
       </c>
@@ -8330,7 +8409,7 @@
         <v>3570</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="15.5">
+    <row r="53" spans="1:15" ht="15.5">
       <c r="A53" s="24" t="s">
         <v>55</v>
       </c>
@@ -8369,8 +8448,11 @@
       <c r="N53" s="63">
         <v>1501</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" ht="15.5">
+      <c r="O53" s="63" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" ht="15.5">
       <c r="A54" s="24" t="s">
         <v>55</v>
       </c>
@@ -8409,8 +8491,11 @@
       <c r="N54" s="63">
         <v>3570</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" ht="15.5">
+      <c r="O54" s="63" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" ht="15.5">
       <c r="A55" s="24" t="s">
         <v>55</v>
       </c>
@@ -8449,8 +8534,11 @@
       <c r="N55" s="63">
         <v>3570</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" ht="15.5">
+      <c r="O55" s="63" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" ht="15.5">
       <c r="A56" s="24" t="s">
         <v>57</v>
       </c>
@@ -8494,7 +8582,7 @@
         <v>3570</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="15.5">
+    <row r="57" spans="1:15" ht="15.5">
       <c r="A57" s="24" t="s">
         <v>74</v>
       </c>
@@ -8531,8 +8619,11 @@
         <v>178</v>
       </c>
       <c r="N57" s="63"/>
-    </row>
-    <row r="58" spans="1:14" ht="15.5">
+      <c r="O57" s="63" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" ht="15.5">
       <c r="A58" s="78" t="s">
         <v>74</v>
       </c>
@@ -8570,7 +8661,7 @@
       </c>
       <c r="N58" s="81"/>
     </row>
-    <row r="59" spans="1:14" ht="15.5">
+    <row r="59" spans="1:15" ht="15.5">
       <c r="A59" s="24" t="s">
         <v>74</v>
       </c>
@@ -8609,8 +8700,11 @@
         <v>178</v>
       </c>
       <c r="N59" s="63"/>
-    </row>
-    <row r="60" spans="1:14" ht="15.5">
+      <c r="O59" s="63" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" ht="15.5">
       <c r="A60" s="24" t="s">
         <v>74</v>
       </c>
@@ -8649,8 +8743,11 @@
       <c r="N60" s="63">
         <v>1411</v>
       </c>
-    </row>
-    <row r="61" spans="1:14" ht="31">
+      <c r="O60" s="63" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" ht="31">
       <c r="A61" s="24" t="s">
         <v>74</v>
       </c>
@@ -8691,8 +8788,11 @@
       <c r="N61" s="63">
         <v>3540</v>
       </c>
-    </row>
-    <row r="62" spans="1:14" ht="15.5">
+      <c r="O61" s="63" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" ht="15.5">
       <c r="A62" s="24" t="s">
         <v>74</v>
       </c>
@@ -8729,8 +8829,11 @@
       <c r="N62" s="63">
         <v>3540</v>
       </c>
-    </row>
-    <row r="63" spans="1:14" ht="15.5">
+      <c r="O62" s="63" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" ht="15.5">
       <c r="A63" s="24" t="s">
         <v>74</v>
       </c>
@@ -8771,8 +8874,11 @@
       <c r="N63" s="63">
         <v>1462</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" ht="15.5">
+      <c r="O63" s="63" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" ht="15.5">
       <c r="A64" s="24" t="s">
         <v>74</v>
       </c>
@@ -8813,8 +8919,11 @@
       <c r="N64" s="63">
         <v>1232</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" ht="15.5">
+      <c r="O64" s="63" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" ht="15.5">
       <c r="A65" s="24" t="s">
         <v>74</v>
       </c>
@@ -8853,8 +8962,11 @@
       <c r="N65" s="63">
         <v>1232</v>
       </c>
-    </row>
-    <row r="66" spans="1:14" ht="15.5">
+      <c r="O65" s="63" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" ht="15.5">
       <c r="A66" s="24" t="s">
         <v>55</v>
       </c>
@@ -8895,8 +9007,11 @@
       <c r="N66" s="63">
         <v>2550</v>
       </c>
-    </row>
-    <row r="67" spans="1:14" ht="15.5">
+      <c r="O66" s="63" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" ht="15.5">
       <c r="A67" s="24" t="s">
         <v>55</v>
       </c>
@@ -8935,8 +9050,11 @@
       <c r="N67" s="63">
         <v>3540</v>
       </c>
-    </row>
-    <row r="68" spans="1:14" ht="15.5">
+      <c r="O67" s="63" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" ht="15.5">
       <c r="A68" s="84" t="s">
         <v>55</v>
       </c>
@@ -8978,7 +9096,7 @@
         <v>3540</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="15.5">
+    <row r="69" spans="1:15" ht="15.5">
       <c r="A69" s="24" t="s">
         <v>57</v>
       </c>
@@ -9022,7 +9140,7 @@
         <v>2501</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="15.5">
+    <row r="70" spans="1:15" ht="15.5">
       <c r="A70" s="24" t="s">
         <v>57</v>
       </c>
@@ -9064,7 +9182,7 @@
         <v>2501</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="15.5">
+    <row r="71" spans="1:15" ht="15.5">
       <c r="A71" s="24" t="s">
         <v>74</v>
       </c>
@@ -9106,7 +9224,7 @@
         <v>2582</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="15.5">
+    <row r="72" spans="1:15" ht="15.5">
       <c r="A72" s="24" t="s">
         <v>74</v>
       </c>
@@ -9146,7 +9264,7 @@
         <v>2530</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="15.5">
+    <row r="73" spans="1:15" ht="15.5">
       <c r="A73" s="24" t="s">
         <v>74</v>
       </c>
@@ -9184,7 +9302,7 @@
         <v>2330</v>
       </c>
     </row>
-    <row r="74" spans="1:14" ht="31">
+    <row r="74" spans="1:15" ht="31">
       <c r="A74" s="24" t="s">
         <v>57</v>
       </c>
@@ -9223,8 +9341,11 @@
       <c r="N74" s="63">
         <v>2432</v>
       </c>
-    </row>
-    <row r="75" spans="1:14" ht="15.5">
+      <c r="O74" s="63" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" ht="15.5">
       <c r="A75" s="24" t="s">
         <v>57</v>
       </c>
@@ -9261,8 +9382,11 @@
       <c r="N75" s="63">
         <v>2432</v>
       </c>
-    </row>
-    <row r="76" spans="1:14" ht="15.5">
+      <c r="O75" s="63" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" ht="15.5">
       <c r="A76" s="24" t="s">
         <v>57</v>
       </c>
@@ -9304,7 +9428,7 @@
         <v>3550</v>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="31">
+    <row r="77" spans="1:15" ht="31">
       <c r="A77" s="24" t="s">
         <v>57</v>
       </c>
@@ -9348,7 +9472,7 @@
         <v>3501</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="31">
+    <row r="78" spans="1:15" ht="31">
       <c r="A78" s="24" t="s">
         <v>57</v>
       </c>
@@ -9388,7 +9512,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="79" spans="1:14" ht="31">
+    <row r="79" spans="1:15" ht="31">
       <c r="A79" s="24" t="s">
         <v>57</v>
       </c>
@@ -9430,7 +9554,7 @@
         <v>2598</v>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="31">
+    <row r="80" spans="1:15" ht="31">
       <c r="A80" s="24" t="s">
         <v>57</v>
       </c>
@@ -10810,7 +10934,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="113" spans="1:14" ht="15.5">
+    <row r="113" spans="1:15" ht="15.5">
       <c r="A113" s="24" t="s">
         <v>74</v>
       </c>
@@ -10852,7 +10976,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="114" spans="1:14" ht="15.5">
+    <row r="114" spans="1:15" ht="15.5">
       <c r="A114" s="24" t="s">
         <v>55</v>
       </c>
@@ -10889,8 +11013,11 @@
       <c r="N114" s="63">
         <v>1411</v>
       </c>
-    </row>
-    <row r="115" spans="1:14" ht="15.5">
+      <c r="O114" s="63" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" ht="15.5">
       <c r="A115" s="24" t="s">
         <v>55</v>
       </c>
@@ -10927,8 +11054,11 @@
       <c r="N115" s="63">
         <v>1360</v>
       </c>
-    </row>
-    <row r="116" spans="1:14" ht="15.5">
+      <c r="O115" s="63" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" ht="15.5">
       <c r="A116" s="24" t="s">
         <v>92</v>
       </c>
@@ -10963,8 +11093,11 @@
         <v>178</v>
       </c>
       <c r="N116" s="63"/>
-    </row>
-    <row r="117" spans="1:14" ht="15.5">
+      <c r="O116" s="63" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" ht="15.5">
       <c r="A117" s="24" t="s">
         <v>92</v>
       </c>
@@ -10997,8 +11130,11 @@
         <v>178</v>
       </c>
       <c r="N117" s="63"/>
-    </row>
-    <row r="118" spans="1:14" ht="15.5">
+      <c r="O117" s="63" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" ht="15.5">
       <c r="A118" s="24" t="s">
         <v>55</v>
       </c>
@@ -11035,8 +11171,11 @@
       <c r="N118" s="63">
         <v>3314</v>
       </c>
-    </row>
-    <row r="119" spans="1:14" ht="15.5">
+      <c r="O118" s="63" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" ht="15.5">
       <c r="A119" s="24" t="s">
         <v>55</v>
       </c>
@@ -11073,8 +11212,11 @@
       <c r="N119" s="63">
         <v>3314</v>
       </c>
-    </row>
-    <row r="120" spans="1:14" ht="15.5">
+      <c r="O119" s="63" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" ht="15.5">
       <c r="A120" s="24" t="s">
         <v>55</v>
       </c>
@@ -11111,8 +11253,11 @@
       <c r="N120" s="63">
         <v>3314</v>
       </c>
-    </row>
-    <row r="121" spans="1:14" ht="15.5">
+      <c r="O120" s="63" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" ht="15.5">
       <c r="A121" s="24" t="s">
         <v>55</v>
       </c>
@@ -11149,8 +11294,11 @@
       <c r="N121" s="63">
         <v>3314</v>
       </c>
-    </row>
-    <row r="122" spans="1:14" ht="15.5">
+      <c r="O121" s="63" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" ht="15.5">
       <c r="A122" s="24" t="s">
         <v>55</v>
       </c>
@@ -11185,8 +11333,11 @@
         <v>178</v>
       </c>
       <c r="N122" s="63"/>
-    </row>
-    <row r="123" spans="1:14" ht="15.5">
+      <c r="O122" s="63" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" ht="15.5">
       <c r="A123" s="24" t="s">
         <v>55</v>
       </c>
@@ -11221,8 +11372,11 @@
         <v>178</v>
       </c>
       <c r="N123" s="63"/>
-    </row>
-    <row r="124" spans="1:14" ht="15.5">
+      <c r="O123" s="63" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" ht="15.5">
       <c r="A124" s="24" t="s">
         <v>55</v>
       </c>
@@ -11257,8 +11411,11 @@
         <v>178</v>
       </c>
       <c r="N124" s="63"/>
-    </row>
-    <row r="125" spans="1:14" ht="15.5">
+      <c r="O124" s="63" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" ht="15.5">
       <c r="A125" s="24" t="s">
         <v>55</v>
       </c>
@@ -11293,8 +11450,11 @@
         <v>178</v>
       </c>
       <c r="N125" s="63"/>
-    </row>
-    <row r="126" spans="1:14" ht="15.5">
+      <c r="O125" s="63" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" ht="15.5">
       <c r="A126" s="24" t="s">
         <v>92</v>
       </c>
@@ -11331,8 +11491,11 @@
       <c r="N126" s="63">
         <v>2515</v>
       </c>
-    </row>
-    <row r="127" spans="1:14" ht="15.5">
+      <c r="O126" s="63" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" ht="15.5">
       <c r="A127" s="24" t="s">
         <v>92</v>
       </c>
@@ -11365,8 +11528,11 @@
         <v>178</v>
       </c>
       <c r="N127" s="63"/>
-    </row>
-    <row r="128" spans="1:14" ht="15.5">
+      <c r="O127" s="63" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" ht="15.5">
       <c r="A128" s="24" t="s">
         <v>92</v>
       </c>
@@ -11399,8 +11565,11 @@
         <v>178</v>
       </c>
       <c r="N128" s="63"/>
-    </row>
-    <row r="129" spans="1:14" ht="15.5">
+      <c r="O128" s="63" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" ht="15.5">
       <c r="A129" s="24" t="s">
         <v>55</v>
       </c>
@@ -11437,8 +11606,11 @@
       <c r="N129" s="63">
         <v>3344</v>
       </c>
-    </row>
-    <row r="130" spans="1:14" ht="15.5">
+      <c r="O129" s="63" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" ht="15.5">
       <c r="A130" s="24" t="s">
         <v>55</v>
       </c>
@@ -11475,8 +11647,11 @@
       <c r="N130" s="63">
         <v>3344</v>
       </c>
-    </row>
-    <row r="131" spans="1:14" ht="15.5">
+      <c r="O130" s="63" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" ht="15.5">
       <c r="A131" s="24" t="s">
         <v>55</v>
       </c>
@@ -11513,8 +11688,11 @@
       <c r="N131" s="63">
         <v>3314</v>
       </c>
-    </row>
-    <row r="132" spans="1:14" ht="15.5">
+      <c r="O131" s="63" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" ht="15.5">
       <c r="A132" s="24" t="s">
         <v>55</v>
       </c>
@@ -11549,8 +11727,11 @@
         <v>178</v>
       </c>
       <c r="N132" s="63"/>
-    </row>
-    <row r="133" spans="1:14" ht="15.5">
+      <c r="O132" s="63" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" ht="15.5">
       <c r="A133" s="24" t="s">
         <v>55</v>
       </c>
@@ -11585,8 +11766,11 @@
         <v>178</v>
       </c>
       <c r="N133" s="63"/>
-    </row>
-    <row r="134" spans="1:14" ht="15.5">
+      <c r="O133" s="63" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" ht="15.5">
       <c r="A134" s="24" t="s">
         <v>55</v>
       </c>
@@ -11625,8 +11809,11 @@
       <c r="N134" s="63">
         <v>1501</v>
       </c>
-    </row>
-    <row r="135" spans="1:14" ht="15.5">
+      <c r="O134" s="63" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" ht="15.5">
       <c r="A135" s="24" t="s">
         <v>55</v>
       </c>
@@ -11665,8 +11852,11 @@
       <c r="N135" s="63">
         <v>3332</v>
       </c>
-    </row>
-    <row r="136" spans="1:14" ht="15.5">
+      <c r="O135" s="63" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" ht="15.5">
       <c r="A136" s="24" t="s">
         <v>55</v>
       </c>
@@ -11699,8 +11889,11 @@
         <v>178</v>
       </c>
       <c r="N136" s="63"/>
-    </row>
-    <row r="137" spans="1:14" ht="15.5">
+      <c r="O136" s="63" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" ht="15.5">
       <c r="A137" s="24" t="s">
         <v>55</v>
       </c>
@@ -11733,8 +11926,11 @@
         <v>178</v>
       </c>
       <c r="N137" s="63"/>
-    </row>
-    <row r="138" spans="1:14" ht="15.5">
+      <c r="O137" s="63" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" ht="15.5">
       <c r="A138" s="24" t="s">
         <v>55</v>
       </c>
@@ -11773,8 +11969,11 @@
       <c r="N138" s="63">
         <v>3332</v>
       </c>
-    </row>
-    <row r="139" spans="1:14" ht="15.5">
+      <c r="O138" s="63" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" ht="15.5">
       <c r="A139" s="24" t="s">
         <v>55</v>
       </c>
@@ -11811,8 +12010,11 @@
       <c r="N139" s="63">
         <v>3332</v>
       </c>
-    </row>
-    <row r="140" spans="1:14" ht="31">
+      <c r="O139" s="63" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" ht="31">
       <c r="A140" s="24" t="s">
         <v>55</v>
       </c>
@@ -11851,8 +12053,11 @@
       <c r="N140" s="63">
         <v>3332</v>
       </c>
-    </row>
-    <row r="141" spans="1:14" ht="15.5">
+      <c r="O140" s="63" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" ht="15.5">
       <c r="A141" s="24" t="s">
         <v>55</v>
       </c>
@@ -11885,8 +12090,11 @@
         <v>178</v>
       </c>
       <c r="N141" s="63"/>
-    </row>
-    <row r="142" spans="1:14" ht="15.5">
+      <c r="O141" s="63" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" ht="15.5">
       <c r="A142" s="24" t="s">
         <v>55</v>
       </c>
@@ -11919,8 +12127,11 @@
         <v>178</v>
       </c>
       <c r="N142" s="63"/>
-    </row>
-    <row r="143" spans="1:14" ht="15.5">
+      <c r="O142" s="63" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" ht="15.5">
       <c r="A143" s="24" t="s">
         <v>55</v>
       </c>
@@ -11953,8 +12164,11 @@
         <v>178</v>
       </c>
       <c r="N143" s="63"/>
-    </row>
-    <row r="144" spans="1:14" ht="15.5">
+      <c r="O143" s="63" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" ht="15.5">
       <c r="A144" s="24" t="s">
         <v>55</v>
       </c>
@@ -11987,8 +12201,11 @@
         <v>178</v>
       </c>
       <c r="N144" s="63"/>
-    </row>
-    <row r="145" spans="1:14" ht="41.25" customHeight="1">
+      <c r="O144" s="63" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" ht="41.25" customHeight="1">
       <c r="A145" s="24"/>
       <c r="B145" s="138" t="s">
         <v>431</v>
@@ -12006,7 +12223,7 @@
       <c r="M145" s="120"/>
       <c r="N145" s="120"/>
     </row>
-    <row r="146" spans="1:14" ht="15.5">
+    <row r="146" spans="1:15" ht="15.5">
       <c r="A146" s="24" t="s">
         <v>92</v>
       </c>
@@ -12041,8 +12258,11 @@
         <v>178</v>
       </c>
       <c r="N146" s="63"/>
-    </row>
-    <row r="147" spans="1:14" ht="15.5">
+      <c r="O146" s="63" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" ht="15.5">
       <c r="A147" s="24" t="s">
         <v>92</v>
       </c>
@@ -12079,8 +12299,11 @@
         <v>178</v>
       </c>
       <c r="N147" s="63"/>
-    </row>
-    <row r="148" spans="1:14" ht="15.5">
+      <c r="O147" s="63" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" ht="15.5">
       <c r="A148" s="24" t="s">
         <v>92</v>
       </c>
@@ -12113,8 +12336,11 @@
         <v>178</v>
       </c>
       <c r="N148" s="63"/>
-    </row>
-    <row r="149" spans="1:14" ht="15.5">
+      <c r="O148" s="63" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" ht="15.5">
       <c r="A149" s="24" t="s">
         <v>406</v>
       </c>
@@ -12149,8 +12375,11 @@
         <v>178</v>
       </c>
       <c r="N149" s="63"/>
-    </row>
-    <row r="150" spans="1:14" ht="15.5">
+      <c r="O149" s="63" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" ht="15.5">
       <c r="A150" s="24" t="s">
         <v>406</v>
       </c>
@@ -12189,8 +12418,11 @@
         <v>178</v>
       </c>
       <c r="N150" s="63"/>
-    </row>
-    <row r="151" spans="1:14" ht="15.5">
+      <c r="O150" s="63" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" ht="15.5">
       <c r="A151" s="24" t="s">
         <v>92</v>
       </c>
@@ -12223,8 +12455,11 @@
         <v>178</v>
       </c>
       <c r="N151" s="63"/>
-    </row>
-    <row r="152" spans="1:14" ht="15.5">
+      <c r="O151" s="63" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" ht="15.5">
       <c r="A152" s="24" t="s">
         <v>406</v>
       </c>
@@ -12261,8 +12496,11 @@
         <v>178</v>
       </c>
       <c r="N152" s="63"/>
-    </row>
-    <row r="153" spans="1:14" ht="15.5">
+      <c r="O152" s="63" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" ht="15.5">
       <c r="A153" s="24" t="s">
         <v>92</v>
       </c>
@@ -12295,8 +12533,11 @@
         <v>178</v>
       </c>
       <c r="N153" s="63"/>
-    </row>
-    <row r="154" spans="1:14" ht="15.5">
+      <c r="O153" s="63" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" ht="15.5">
       <c r="A154" s="24" t="s">
         <v>406</v>
       </c>
@@ -12333,8 +12574,11 @@
         <v>178</v>
       </c>
       <c r="N154" s="63"/>
-    </row>
-    <row r="155" spans="1:14" ht="15.5">
+      <c r="O154" s="63" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" ht="15.5">
       <c r="A155" s="24" t="s">
         <v>92</v>
       </c>
@@ -12371,8 +12615,11 @@
         <v>178</v>
       </c>
       <c r="N155" s="63"/>
-    </row>
-    <row r="156" spans="1:14" ht="15.5">
+      <c r="O155" s="63" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" ht="15.5">
       <c r="A156" s="24" t="s">
         <v>92</v>
       </c>
@@ -12409,8 +12656,11 @@
         <v>178</v>
       </c>
       <c r="N156" s="63"/>
-    </row>
-    <row r="157" spans="1:14" ht="15.5">
+      <c r="O156" s="63" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" ht="15.5">
       <c r="A157" s="24" t="s">
         <v>92</v>
       </c>
@@ -12445,6 +12695,9 @@
         <v>178</v>
       </c>
       <c r="N157" s="63"/>
+      <c r="O157" s="63" t="s">
+        <v>456</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="16">

--- a/sample_data/Tutor_Copy_-_Fall_2026_Acceptance___Placement_Choices_for_LRC.xlsx
+++ b/sample_data/Tutor_Copy_-_Fall_2026_Acceptance___Placement_Choices_for_LRC.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\tutor_assignment_app\sample_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andre\tutor_assignment_app\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A6DE31-6C68-43E3-991F-4B30EC5E290A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F74B6C3-26D7-4F78-AD23-26A6A770E4A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Placements (Tutors Please Revie" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2605" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2603" uniqueCount="468">
   <si>
     <t>Tutors: Please review your placement(s) and Accept no later than Sunday Aug 16
 If for some reason your availability has changed, you must email LRC Pro Staff ASAP
@@ -595,9 +595,6 @@
     <t>Vaughn, Ariel</t>
   </si>
   <si>
-    <t>Ryan Moses (CAT like last sem!)</t>
-  </si>
-  <si>
     <t>karen galvan</t>
   </si>
   <si>
@@ -1467,9 +1464,6 @@
     <t>COMP 262 - A</t>
   </si>
   <si>
-    <t>ESRM 203 - A</t>
-  </si>
-  <si>
     <t>PSY 300 - A</t>
   </si>
   <si>
@@ -1501,6 +1495,21 @@
   </si>
   <si>
     <t>PSY 314 - D</t>
+  </si>
+  <si>
+    <t>PSY 300 - EA</t>
+  </si>
+  <si>
+    <t>PSY 300 - EB</t>
+  </si>
+  <si>
+    <t>PSY 301 - EA</t>
+  </si>
+  <si>
+    <t>PSY 301 - EB</t>
+  </si>
+  <si>
+    <t>PSY 314 - EA</t>
   </si>
 </sst>
 </file>
@@ -2482,47 +2491,47 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="9" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="9" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="9" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="9" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="9" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="9" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="7" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="9" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="9" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="9" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="9" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="9" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2855,7 +2864,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="14">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="147" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="120"/>
@@ -2864,12 +2873,12 @@
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="127" t="s">
+      <c r="F1" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="128"/>
-      <c r="H1" s="128"/>
-      <c r="I1" s="129"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="127"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
@@ -2883,10 +2892,10 @@
       <c r="C2" s="120"/>
       <c r="D2" s="120"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="131"/>
-      <c r="H2" s="131"/>
-      <c r="I2" s="132"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="128"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -2905,7 +2914,7 @@
       </c>
       <c r="G3" s="120"/>
       <c r="H3" s="120"/>
-      <c r="I3" s="121"/>
+      <c r="I3" s="134"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -2919,12 +2928,12 @@
       <c r="C4" s="120"/>
       <c r="D4" s="120"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="134" t="s">
+      <c r="F4" s="135" t="s">
         <v>10</v>
       </c>
       <c r="G4" s="120"/>
       <c r="H4" s="120"/>
-      <c r="I4" s="121"/>
+      <c r="I4" s="134"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -2938,12 +2947,12 @@
       <c r="C5" s="120"/>
       <c r="D5" s="120"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="135" t="s">
+      <c r="F5" s="136" t="s">
         <v>12</v>
       </c>
       <c r="G5" s="120"/>
       <c r="H5" s="120"/>
-      <c r="I5" s="121"/>
+      <c r="I5" s="134"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -2957,12 +2966,12 @@
       <c r="C6" s="120"/>
       <c r="D6" s="120"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="136" t="s">
+      <c r="F6" s="137" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="131"/>
-      <c r="H6" s="131"/>
-      <c r="I6" s="132"/>
+      <c r="G6" s="125"/>
+      <c r="H6" s="125"/>
+      <c r="I6" s="128"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -2976,12 +2985,12 @@
       <c r="C7" s="120"/>
       <c r="D7" s="120"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="137" t="s">
+      <c r="F7" s="138" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="131"/>
-      <c r="H7" s="131"/>
-      <c r="I7" s="132"/>
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="128"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -2995,12 +3004,12 @@
       <c r="C8" s="120"/>
       <c r="D8" s="120"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="119" t="s">
+      <c r="F8" s="139" t="s">
         <v>27</v>
       </c>
       <c r="G8" s="120"/>
       <c r="H8" s="120"/>
-      <c r="I8" s="121"/>
+      <c r="I8" s="134"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -3014,12 +3023,12 @@
       <c r="C9" s="120"/>
       <c r="D9" s="120"/>
       <c r="E9" s="1"/>
-      <c r="F9" s="122" t="s">
+      <c r="F9" s="142" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="123"/>
-      <c r="H9" s="123"/>
-      <c r="I9" s="124"/>
+      <c r="G9" s="143"/>
+      <c r="H9" s="143"/>
+      <c r="I9" s="144"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -3849,7 +3858,7 @@
         <v>74</v>
       </c>
       <c r="B29" s="57" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C29" s="26" t="s">
         <v>59</v>
@@ -3857,22 +3866,22 @@
       <c r="D29" s="27"/>
       <c r="E29" s="27"/>
       <c r="F29" s="59" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G29" s="61">
         <v>1</v>
       </c>
       <c r="H29" s="59" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I29" s="33" t="s">
         <v>100</v>
       </c>
       <c r="J29" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="K29" s="33" t="s">
         <v>172</v>
-      </c>
-      <c r="K29" s="33" t="s">
-        <v>173</v>
       </c>
       <c r="L29" s="33" t="s">
         <v>71</v>
@@ -3892,7 +3901,7 @@
         <v>74</v>
       </c>
       <c r="B30" s="57" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C30" s="26" t="s">
         <v>59</v>
@@ -3900,22 +3909,22 @@
       <c r="D30" s="27"/>
       <c r="E30" s="27"/>
       <c r="F30" s="59" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G30" s="61">
         <v>1</v>
       </c>
       <c r="H30" s="59" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I30" s="33" t="s">
         <v>100</v>
       </c>
       <c r="J30" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="K30" s="33" t="s">
         <v>172</v>
-      </c>
-      <c r="K30" s="33" t="s">
-        <v>173</v>
       </c>
       <c r="L30" s="33" t="s">
         <v>71</v>
@@ -3935,7 +3944,7 @@
         <v>74</v>
       </c>
       <c r="B31" s="57" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C31" s="26" t="s">
         <v>59</v>
@@ -3943,13 +3952,13 @@
       <c r="D31" s="26"/>
       <c r="E31" s="26"/>
       <c r="F31" s="59" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G31" s="61">
         <v>1</v>
       </c>
       <c r="H31" s="59" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I31" s="33" t="s">
         <v>68</v>
@@ -3958,7 +3967,7 @@
         <v>105</v>
       </c>
       <c r="K31" s="33" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L31" s="33" t="s">
         <v>71</v>
@@ -3978,7 +3987,7 @@
         <v>74</v>
       </c>
       <c r="B32" s="57" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C32" s="26" t="s">
         <v>59</v>
@@ -3986,13 +3995,13 @@
       <c r="D32" s="26"/>
       <c r="E32" s="26"/>
       <c r="F32" s="59" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G32" s="61">
         <v>1</v>
       </c>
       <c r="H32" s="59" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I32" s="33" t="s">
         <v>68</v>
@@ -4001,7 +4010,7 @@
         <v>105</v>
       </c>
       <c r="K32" s="33" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L32" s="33" t="s">
         <v>71</v>
@@ -4021,7 +4030,7 @@
         <v>74</v>
       </c>
       <c r="B33" s="57" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C33" s="26" t="s">
         <v>59</v>
@@ -4029,13 +4038,13 @@
       <c r="D33" s="58"/>
       <c r="E33" s="58"/>
       <c r="F33" s="59" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G33" s="61">
         <v>1</v>
       </c>
       <c r="H33" s="59" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I33" s="33" t="s">
         <v>100</v>
@@ -4044,7 +4053,7 @@
         <v>111</v>
       </c>
       <c r="K33" s="33" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L33" s="33" t="s">
         <v>71</v>
@@ -4064,7 +4073,7 @@
         <v>74</v>
       </c>
       <c r="B34" s="57" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C34" s="26" t="s">
         <v>59</v>
@@ -4072,13 +4081,13 @@
       <c r="D34" s="58"/>
       <c r="E34" s="58"/>
       <c r="F34" s="59" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G34" s="61">
         <v>1</v>
       </c>
       <c r="H34" s="59" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I34" s="33" t="s">
         <v>100</v>
@@ -4087,7 +4096,7 @@
         <v>111</v>
       </c>
       <c r="K34" s="33" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L34" s="33" t="s">
         <v>71</v>
@@ -4107,7 +4116,7 @@
         <v>57</v>
       </c>
       <c r="B35" s="39" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C35" s="26" t="s">
         <v>59</v>
@@ -4115,13 +4124,13 @@
       <c r="D35" s="58"/>
       <c r="E35" s="58"/>
       <c r="F35" s="43" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G35" s="44">
         <v>1</v>
       </c>
       <c r="H35" s="43" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I35" s="33" t="s">
         <v>100</v>
@@ -4130,7 +4139,7 @@
         <v>105</v>
       </c>
       <c r="K35" s="33" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L35" s="33" t="s">
         <v>71</v>
@@ -4150,7 +4159,7 @@
         <v>57</v>
       </c>
       <c r="B36" s="39" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C36" s="26" t="s">
         <v>59</v>
@@ -4158,22 +4167,22 @@
       <c r="D36" s="58"/>
       <c r="E36" s="58"/>
       <c r="F36" s="43" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G36" s="44">
         <v>1</v>
       </c>
       <c r="H36" s="43" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I36" s="33" t="s">
         <v>100</v>
       </c>
       <c r="J36" s="33" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K36" s="33" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L36" s="33" t="s">
         <v>71</v>
@@ -4193,7 +4202,7 @@
         <v>57</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C37" s="26" t="s">
         <v>59</v>
@@ -4201,22 +4210,22 @@
       <c r="D37" s="58"/>
       <c r="E37" s="58"/>
       <c r="F37" s="43" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G37" s="44">
         <v>1</v>
       </c>
       <c r="H37" s="43" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I37" s="33" t="s">
         <v>100</v>
       </c>
       <c r="J37" s="33" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K37" s="33" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L37" s="33" t="s">
         <v>71</v>
@@ -4244,31 +4253,31 @@
       <c r="D38" s="27"/>
       <c r="E38" s="27"/>
       <c r="F38" s="59" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G38" s="61">
         <v>2</v>
       </c>
       <c r="H38" s="59" t="s">
+        <v>206</v>
+      </c>
+      <c r="I38" s="33" t="s">
         <v>207</v>
-      </c>
-      <c r="I38" s="33" t="s">
-        <v>208</v>
       </c>
       <c r="J38" s="33" t="s">
         <v>143</v>
       </c>
       <c r="K38" s="33" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L38" s="33" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M38" s="33" t="s">
         <v>72</v>
       </c>
       <c r="N38" s="33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O38" s="77"/>
     </row>
@@ -4285,31 +4294,31 @@
       <c r="D39" s="27"/>
       <c r="E39" s="27"/>
       <c r="F39" s="59" t="s">
+        <v>205</v>
+      </c>
+      <c r="G39" s="59" t="s">
+        <v>214</v>
+      </c>
+      <c r="H39" s="59" t="s">
         <v>206</v>
-      </c>
-      <c r="G39" s="59" t="s">
-        <v>215</v>
-      </c>
-      <c r="H39" s="59" t="s">
-        <v>207</v>
       </c>
       <c r="I39" s="33" t="s">
         <v>128</v>
       </c>
       <c r="J39" s="33" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K39" s="33" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L39" s="33" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M39" s="33" t="s">
         <v>72</v>
       </c>
       <c r="N39" s="33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O39" s="77"/>
     </row>
@@ -4318,7 +4327,7 @@
         <v>74</v>
       </c>
       <c r="B40" s="57" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C40" s="26" t="s">
         <v>59</v>
@@ -4326,22 +4335,22 @@
       <c r="D40" s="58"/>
       <c r="E40" s="58"/>
       <c r="F40" s="59" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G40" s="61">
         <v>1</v>
       </c>
       <c r="H40" s="59" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I40" s="33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J40" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="K40" s="33" t="s">
         <v>223</v>
-      </c>
-      <c r="K40" s="33" t="s">
-        <v>224</v>
       </c>
       <c r="L40" s="33" t="s">
         <v>71</v>
@@ -4361,7 +4370,7 @@
         <v>74</v>
       </c>
       <c r="B41" s="57" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C41" s="26" t="s">
         <v>59</v>
@@ -4369,22 +4378,22 @@
       <c r="D41" s="58"/>
       <c r="E41" s="58"/>
       <c r="F41" s="59" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G41" s="59" t="s">
         <v>136</v>
       </c>
       <c r="H41" s="59" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I41" s="33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J41" s="33" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K41" s="33" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L41" s="33" t="s">
         <v>71</v>
@@ -4404,7 +4413,7 @@
         <v>74</v>
       </c>
       <c r="B42" s="57" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C42" s="26" t="s">
         <v>59</v>
@@ -4412,13 +4421,13 @@
       <c r="D42" s="27"/>
       <c r="E42" s="27"/>
       <c r="F42" s="59" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G42" s="59" t="s">
         <v>141</v>
       </c>
       <c r="H42" s="59" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I42" s="33" t="s">
         <v>82</v>
@@ -4427,7 +4436,7 @@
         <v>143</v>
       </c>
       <c r="K42" s="33" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L42" s="33" t="s">
         <v>71</v>
@@ -4447,7 +4456,7 @@
         <v>57</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C43" s="26" t="s">
         <v>59</v>
@@ -4455,13 +4464,13 @@
       <c r="D43" s="58"/>
       <c r="E43" s="58"/>
       <c r="F43" s="43" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G43" s="44">
         <v>1</v>
       </c>
       <c r="H43" s="43" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I43" s="33" t="s">
         <v>68</v>
@@ -4470,7 +4479,7 @@
         <v>142</v>
       </c>
       <c r="K43" s="33" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L43" s="33" t="s">
         <v>71</v>
@@ -4498,13 +4507,13 @@
       <c r="D44" s="27"/>
       <c r="E44" s="27"/>
       <c r="F44" s="43" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G44" s="44">
         <v>2</v>
       </c>
       <c r="H44" s="43" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I44" s="33" t="s">
         <v>68</v>
@@ -4513,7 +4522,7 @@
         <v>69</v>
       </c>
       <c r="K44" s="33" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L44" s="33" t="s">
         <v>71</v>
@@ -4541,22 +4550,22 @@
       <c r="D45" s="27"/>
       <c r="E45" s="27"/>
       <c r="F45" s="66" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G45" s="67">
         <v>1</v>
       </c>
       <c r="H45" s="66" t="s">
+        <v>237</v>
+      </c>
+      <c r="I45" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="J45" s="33" t="s">
         <v>238</v>
       </c>
-      <c r="I45" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="J45" s="33" t="s">
+      <c r="K45" s="33" t="s">
         <v>239</v>
-      </c>
-      <c r="K45" s="33" t="s">
-        <v>240</v>
       </c>
       <c r="L45" s="33" t="s">
         <v>71</v>
@@ -4584,22 +4593,22 @@
       <c r="D46" s="58"/>
       <c r="E46" s="58"/>
       <c r="F46" s="66" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G46" s="67">
         <v>2</v>
       </c>
       <c r="H46" s="66" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I46" s="33" t="s">
         <v>137</v>
       </c>
       <c r="J46" s="33" t="s">
+        <v>238</v>
+      </c>
+      <c r="K46" s="33" t="s">
         <v>239</v>
-      </c>
-      <c r="K46" s="33" t="s">
-        <v>240</v>
       </c>
       <c r="L46" s="33" t="s">
         <v>71</v>
@@ -4627,22 +4636,22 @@
       <c r="D47" s="27"/>
       <c r="E47" s="27"/>
       <c r="F47" s="43" t="s">
+        <v>243</v>
+      </c>
+      <c r="G47" s="43" t="s">
         <v>244</v>
       </c>
-      <c r="G47" s="43" t="s">
+      <c r="H47" s="43" t="s">
         <v>245</v>
-      </c>
-      <c r="H47" s="43" t="s">
-        <v>246</v>
       </c>
       <c r="I47" s="33" t="s">
         <v>68</v>
       </c>
       <c r="J47" s="33" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K47" s="33" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L47" s="33" t="s">
         <v>71</v>
@@ -4662,7 +4671,7 @@
         <v>57</v>
       </c>
       <c r="B48" s="39" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C48" s="26" t="s">
         <v>59</v>
@@ -4670,22 +4679,22 @@
       <c r="D48" s="27"/>
       <c r="E48" s="27"/>
       <c r="F48" s="43" t="s">
+        <v>243</v>
+      </c>
+      <c r="G48" s="43" t="s">
         <v>244</v>
       </c>
-      <c r="G48" s="43" t="s">
+      <c r="H48" s="43" t="s">
         <v>245</v>
-      </c>
-      <c r="H48" s="43" t="s">
-        <v>246</v>
       </c>
       <c r="I48" s="33" t="s">
         <v>68</v>
       </c>
       <c r="J48" s="33" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K48" s="33" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L48" s="33" t="s">
         <v>71</v>
@@ -4705,7 +4714,7 @@
         <v>57</v>
       </c>
       <c r="B49" s="39" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C49" s="26" t="s">
         <v>59</v>
@@ -4713,22 +4722,22 @@
       <c r="D49" s="26"/>
       <c r="E49" s="26"/>
       <c r="F49" s="43" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G49" s="43" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H49" s="43" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I49" s="33" t="s">
         <v>100</v>
       </c>
       <c r="J49" s="33" t="s">
+        <v>252</v>
+      </c>
+      <c r="K49" s="33" t="s">
         <v>253</v>
-      </c>
-      <c r="K49" s="33" t="s">
-        <v>254</v>
       </c>
       <c r="L49" s="33" t="s">
         <v>71</v>
@@ -4748,7 +4757,7 @@
         <v>57</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C50" s="26" t="s">
         <v>59</v>
@@ -4756,19 +4765,19 @@
       <c r="D50" s="27"/>
       <c r="E50" s="27"/>
       <c r="F50" s="43" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G50" s="43" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H50" s="43" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I50" s="33" t="s">
         <v>68</v>
       </c>
       <c r="J50" s="33" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K50" s="33" t="s">
         <v>70</v>
@@ -4799,22 +4808,22 @@
       <c r="D51" s="58"/>
       <c r="E51" s="58"/>
       <c r="F51" s="43" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G51" s="44">
         <v>1</v>
       </c>
       <c r="H51" s="43" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I51" s="33" t="s">
         <v>68</v>
       </c>
       <c r="J51" s="33" t="s">
+        <v>262</v>
+      </c>
+      <c r="K51" s="33" t="s">
         <v>263</v>
-      </c>
-      <c r="K51" s="33" t="s">
-        <v>264</v>
       </c>
       <c r="L51" s="33" t="s">
         <v>71</v>
@@ -4834,7 +4843,7 @@
         <v>57</v>
       </c>
       <c r="B52" s="39" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C52" s="26" t="s">
         <v>59</v>
@@ -4842,22 +4851,22 @@
       <c r="D52" s="58"/>
       <c r="E52" s="58"/>
       <c r="F52" s="43" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G52" s="44">
         <v>2</v>
       </c>
       <c r="H52" s="43" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I52" s="33" t="s">
         <v>100</v>
       </c>
       <c r="J52" s="33" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K52" s="33" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L52" s="33" t="s">
         <v>71</v>
@@ -4877,7 +4886,7 @@
         <v>57</v>
       </c>
       <c r="B53" s="39" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C53" s="26" t="s">
         <v>59</v>
@@ -4885,22 +4894,22 @@
       <c r="D53" s="58"/>
       <c r="E53" s="58"/>
       <c r="F53" s="43" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G53" s="44">
         <v>3</v>
       </c>
       <c r="H53" s="43" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I53" s="33" t="s">
         <v>100</v>
       </c>
       <c r="J53" s="33" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K53" s="33" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L53" s="33" t="s">
         <v>71</v>
@@ -4920,7 +4929,7 @@
         <v>57</v>
       </c>
       <c r="B54" s="39" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C54" s="26" t="s">
         <v>59</v>
@@ -4928,22 +4937,22 @@
       <c r="D54" s="58"/>
       <c r="E54" s="58"/>
       <c r="F54" s="43" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G54" s="44">
         <v>1</v>
       </c>
       <c r="H54" s="43" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I54" s="33" t="s">
         <v>68</v>
       </c>
       <c r="J54" s="33" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K54" s="33" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L54" s="33" t="s">
         <v>71</v>
@@ -4963,28 +4972,28 @@
         <v>57</v>
       </c>
       <c r="B55" s="39" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C55" s="26" t="s">
         <v>59</v>
       </c>
       <c r="F55" s="43" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G55" s="44">
         <v>2</v>
       </c>
       <c r="H55" s="43" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I55" s="33" t="s">
         <v>100</v>
       </c>
       <c r="J55" s="33" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K55" s="33" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L55" s="33" t="s">
         <v>71</v>
@@ -5004,7 +5013,7 @@
         <v>57</v>
       </c>
       <c r="B56" s="39" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C56" s="26" t="s">
         <v>59</v>
@@ -5012,22 +5021,22 @@
       <c r="D56" s="58"/>
       <c r="E56" s="58"/>
       <c r="F56" s="43" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G56" s="44">
         <v>3</v>
       </c>
       <c r="H56" s="43" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I56" s="33" t="s">
         <v>100</v>
       </c>
       <c r="J56" s="33" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K56" s="66" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L56" s="33" t="s">
         <v>71</v>
@@ -5047,7 +5056,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="39" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C57" s="26" t="s">
         <v>59</v>
@@ -5055,22 +5064,22 @@
       <c r="D57" s="58"/>
       <c r="E57" s="58"/>
       <c r="F57" s="43" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G57" s="44">
         <v>1</v>
       </c>
       <c r="H57" s="43" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I57" s="33" t="s">
         <v>100</v>
       </c>
       <c r="J57" s="33" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K57" s="33" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L57" s="33" t="s">
         <v>71</v>
@@ -5090,7 +5099,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="89" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C58" s="26" t="s">
         <v>59</v>
@@ -5098,22 +5107,22 @@
       <c r="D58" s="58"/>
       <c r="E58" s="58"/>
       <c r="F58" s="90" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G58" s="91">
         <v>1</v>
       </c>
       <c r="H58" s="90" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I58" s="33" t="s">
         <v>68</v>
       </c>
       <c r="J58" s="33" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K58" s="33" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L58" s="33" t="s">
         <v>71</v>
@@ -5133,7 +5142,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="39" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C59" s="26" t="s">
         <v>59</v>
@@ -5141,22 +5150,22 @@
       <c r="D59" s="58"/>
       <c r="E59" s="58"/>
       <c r="F59" s="43" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G59" s="44">
         <v>3</v>
       </c>
       <c r="H59" s="43" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I59" s="33" t="s">
         <v>68</v>
       </c>
       <c r="J59" s="33" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K59" s="33" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L59" s="33" t="s">
         <v>71</v>
@@ -5176,7 +5185,7 @@
         <v>57</v>
       </c>
       <c r="B60" s="92" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C60" s="26" t="s">
         <v>59</v>
@@ -5184,22 +5193,22 @@
       <c r="D60" s="58"/>
       <c r="E60" s="58"/>
       <c r="F60" s="93" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G60" s="94">
         <v>4</v>
       </c>
       <c r="H60" s="93" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I60" s="33" t="s">
         <v>100</v>
       </c>
       <c r="J60" s="33" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K60" s="33" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L60" s="33" t="s">
         <v>71</v>
@@ -5219,7 +5228,7 @@
         <v>74</v>
       </c>
       <c r="B61" s="57" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C61" s="26" t="s">
         <v>59</v>
@@ -5227,22 +5236,22 @@
       <c r="D61" s="58"/>
       <c r="E61" s="58"/>
       <c r="F61" s="59" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G61" s="61">
         <v>1</v>
       </c>
       <c r="H61" s="59" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I61" s="33" t="s">
         <v>100</v>
       </c>
       <c r="J61" s="33" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K61" s="33" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L61" s="33" t="s">
         <v>71</v>
@@ -5262,7 +5271,7 @@
         <v>57</v>
       </c>
       <c r="B62" s="39" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C62" s="26" t="s">
         <v>59</v>
@@ -5270,22 +5279,22 @@
       <c r="D62" s="27"/>
       <c r="E62" s="27"/>
       <c r="F62" s="90" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G62" s="91">
         <v>2</v>
       </c>
       <c r="H62" s="90" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I62" s="33" t="s">
         <v>100</v>
       </c>
       <c r="J62" s="33" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K62" s="33" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L62" s="33" t="s">
         <v>71</v>
@@ -5305,7 +5314,7 @@
         <v>57</v>
       </c>
       <c r="B63" s="39" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C63" s="26" t="s">
         <v>59</v>
@@ -5319,7 +5328,7 @@
         <v>1</v>
       </c>
       <c r="H63" s="43" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I63" s="33" t="s">
         <v>100</v>
@@ -5328,7 +5337,7 @@
         <v>101</v>
       </c>
       <c r="K63" s="33" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L63" s="33" t="s">
         <v>71</v>
@@ -5348,7 +5357,7 @@
         <v>92</v>
       </c>
       <c r="B64" s="64" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C64" s="26" t="s">
         <v>59</v>
@@ -5362,7 +5371,7 @@
         <v>2</v>
       </c>
       <c r="H64" s="43" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I64" s="33" t="s">
         <v>100</v>
@@ -5371,7 +5380,7 @@
         <v>69</v>
       </c>
       <c r="K64" s="33" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L64" s="33" t="s">
         <v>71</v>
@@ -5399,13 +5408,13 @@
       <c r="D65" s="26"/>
       <c r="E65" s="26"/>
       <c r="F65" s="43" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G65" s="44">
         <v>1</v>
       </c>
       <c r="H65" s="43" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I65" s="33" t="s">
         <v>68</v>
@@ -5414,7 +5423,7 @@
         <v>142</v>
       </c>
       <c r="K65" s="33" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L65" s="33" t="s">
         <v>71</v>
@@ -5434,7 +5443,7 @@
         <v>57</v>
       </c>
       <c r="B66" s="89" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C66" s="26" t="s">
         <v>59</v>
@@ -5442,22 +5451,22 @@
       <c r="D66" s="58"/>
       <c r="E66" s="58"/>
       <c r="F66" s="43" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G66" s="44">
         <v>2</v>
       </c>
       <c r="H66" s="43" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I66" s="33" t="s">
         <v>68</v>
       </c>
       <c r="J66" s="33" t="s">
+        <v>317</v>
+      </c>
+      <c r="K66" s="33" t="s">
         <v>318</v>
-      </c>
-      <c r="K66" s="33" t="s">
-        <v>319</v>
       </c>
       <c r="L66" s="33" t="s">
         <v>71</v>
@@ -5477,28 +5486,28 @@
         <v>57</v>
       </c>
       <c r="B67" s="65" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C67" s="26"/>
       <c r="D67" s="27"/>
       <c r="E67" s="27"/>
       <c r="F67" s="66" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G67" s="67">
         <v>1</v>
       </c>
       <c r="H67" s="66" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I67" s="33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J67" s="33" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K67" s="33" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L67" s="33" t="s">
         <v>71</v>
@@ -5518,7 +5527,7 @@
         <v>57</v>
       </c>
       <c r="B68" s="39" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C68" s="26" t="s">
         <v>59</v>
@@ -5526,22 +5535,22 @@
       <c r="D68" s="58"/>
       <c r="E68" s="58"/>
       <c r="F68" s="43" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G68" s="44">
         <v>2</v>
       </c>
       <c r="H68" s="43" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I68" s="33" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J68" s="33" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K68" s="33" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L68" s="33" t="s">
         <v>71</v>
@@ -5569,13 +5578,13 @@
       <c r="D69" s="58"/>
       <c r="E69" s="58"/>
       <c r="F69" s="59" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G69" s="61">
         <v>2</v>
       </c>
       <c r="H69" s="59" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I69" s="33" t="s">
         <v>68</v>
@@ -5584,7 +5593,7 @@
         <v>69</v>
       </c>
       <c r="K69" s="33" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L69" s="33" t="s">
         <v>71</v>
@@ -5612,13 +5621,13 @@
       <c r="D70" s="58"/>
       <c r="E70" s="58"/>
       <c r="F70" s="59" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G70" s="61">
         <v>1</v>
       </c>
       <c r="H70" s="59" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I70" s="33" t="s">
         <v>68</v>
@@ -5627,7 +5636,7 @@
         <v>142</v>
       </c>
       <c r="K70" s="33" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L70" s="33" t="s">
         <v>71</v>
@@ -5647,7 +5656,7 @@
         <v>74</v>
       </c>
       <c r="B71" s="57" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C71" s="26" t="s">
         <v>59</v>
@@ -5655,13 +5664,13 @@
       <c r="D71" s="58"/>
       <c r="E71" s="58"/>
       <c r="F71" s="59" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G71" s="61">
         <v>2</v>
       </c>
       <c r="H71" s="59" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I71" s="33" t="s">
         <v>68</v>
@@ -5670,7 +5679,7 @@
         <v>142</v>
       </c>
       <c r="K71" s="33" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L71" s="33" t="s">
         <v>71</v>
@@ -5698,13 +5707,13 @@
       <c r="D72" s="58"/>
       <c r="E72" s="58"/>
       <c r="F72" s="59" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G72" s="61">
         <v>1</v>
       </c>
       <c r="H72" s="59" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I72" s="33" t="s">
         <v>100</v>
@@ -5713,7 +5722,7 @@
         <v>69</v>
       </c>
       <c r="K72" s="33" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L72" s="33" t="s">
         <v>71</v>
@@ -5728,12 +5737,12 @@
         <v>3550</v>
       </c>
     </row>
-    <row r="73" spans="1:15" ht="15.5">
+    <row r="73" spans="1:15" ht="31">
       <c r="A73" s="37" t="s">
         <v>92</v>
       </c>
       <c r="B73" s="64" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C73" s="26" t="s">
         <v>59</v>
@@ -5741,22 +5750,22 @@
       <c r="D73" s="58"/>
       <c r="E73" s="58"/>
       <c r="F73" s="59" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G73" s="61">
         <v>2</v>
       </c>
       <c r="H73" s="59" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I73" s="33" t="s">
         <v>68</v>
       </c>
       <c r="J73" s="33" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="K73" s="33" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L73" s="33" t="s">
         <v>71</v>
@@ -5776,28 +5785,28 @@
         <v>92</v>
       </c>
       <c r="B74" s="64" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C74" s="26"/>
       <c r="D74" s="58"/>
       <c r="E74" s="58"/>
       <c r="F74" s="59" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G74" s="61">
         <v>1</v>
       </c>
       <c r="H74" s="59" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="I74" s="33" t="s">
         <v>137</v>
       </c>
       <c r="J74" s="33" t="s">
+        <v>351</v>
+      </c>
+      <c r="K74" s="33" t="s">
         <v>352</v>
-      </c>
-      <c r="K74" s="33" t="s">
-        <v>353</v>
       </c>
       <c r="L74" s="33" t="s">
         <v>71</v>
@@ -5817,7 +5826,7 @@
         <v>92</v>
       </c>
       <c r="B75" s="64" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C75" s="26" t="s">
         <v>59</v>
@@ -5825,22 +5834,22 @@
       <c r="D75" s="58"/>
       <c r="E75" s="58"/>
       <c r="F75" s="59" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G75" s="61">
         <v>1</v>
       </c>
       <c r="H75" s="59" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="I75" s="33" t="s">
         <v>137</v>
       </c>
       <c r="J75" s="33" t="s">
+        <v>351</v>
+      </c>
+      <c r="K75" s="33" t="s">
         <v>352</v>
-      </c>
-      <c r="K75" s="33" t="s">
-        <v>353</v>
       </c>
       <c r="L75" s="33" t="s">
         <v>71</v>
@@ -5860,7 +5869,7 @@
         <v>92</v>
       </c>
       <c r="B76" s="64" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C76" s="26" t="s">
         <v>59</v>
@@ -5868,22 +5877,22 @@
       <c r="D76" s="58"/>
       <c r="E76" s="58"/>
       <c r="F76" s="59" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G76" s="61">
         <v>1</v>
       </c>
       <c r="H76" s="59" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="I76" s="33" t="s">
         <v>137</v>
       </c>
       <c r="J76" s="33" t="s">
+        <v>351</v>
+      </c>
+      <c r="K76" s="33" t="s">
         <v>352</v>
-      </c>
-      <c r="K76" s="33" t="s">
-        <v>353</v>
       </c>
       <c r="L76" s="33" t="s">
         <v>71</v>
@@ -5903,7 +5912,7 @@
         <v>74</v>
       </c>
       <c r="B77" s="57" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C77" s="26" t="s">
         <v>59</v>
@@ -5911,22 +5920,22 @@
       <c r="D77" s="58"/>
       <c r="E77" s="58"/>
       <c r="F77" s="59" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G77" s="61">
         <v>1</v>
       </c>
       <c r="H77" s="59" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="I77" s="33" t="s">
         <v>68</v>
       </c>
       <c r="J77" s="33" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K77" s="33" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="L77" s="33" t="s">
         <v>71</v>
@@ -5946,7 +5955,7 @@
         <v>74</v>
       </c>
       <c r="B78" s="57" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C78" s="26" t="s">
         <v>59</v>
@@ -5954,13 +5963,13 @@
       <c r="D78" s="58"/>
       <c r="E78" s="58"/>
       <c r="F78" s="59" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G78" s="61">
         <v>1</v>
       </c>
       <c r="H78" s="59" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I78" s="33" t="s">
         <v>68</v>
@@ -5969,7 +5978,7 @@
         <v>69</v>
       </c>
       <c r="K78" s="33" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="L78" s="33" t="s">
         <v>71</v>
@@ -5989,7 +5998,7 @@
         <v>74</v>
       </c>
       <c r="B79" s="57" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C79" s="26" t="s">
         <v>59</v>
@@ -5997,13 +6006,13 @@
       <c r="D79" s="58"/>
       <c r="E79" s="58"/>
       <c r="F79" s="59" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G79" s="61">
         <v>1</v>
       </c>
       <c r="H79" s="59" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="I79" s="33" t="s">
         <v>68</v>
@@ -6012,7 +6021,7 @@
         <v>142</v>
       </c>
       <c r="K79" s="33" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="L79" s="33" t="s">
         <v>71</v>
@@ -6032,7 +6041,7 @@
         <v>74</v>
       </c>
       <c r="B80" s="57" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C80" s="26" t="s">
         <v>59</v>
@@ -6040,13 +6049,13 @@
       <c r="D80" s="58"/>
       <c r="E80" s="58"/>
       <c r="F80" s="59" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G80" s="61">
         <v>1</v>
       </c>
       <c r="H80" s="59" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="I80" s="33" t="s">
         <v>68</v>
@@ -6055,7 +6064,7 @@
         <v>69</v>
       </c>
       <c r="K80" s="33" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="L80" s="33" t="s">
         <v>71</v>
@@ -6073,8 +6082,8 @@
     <row r="81" spans="1:15" ht="16.5">
       <c r="A81" s="97"/>
       <c r="B81" s="98"/>
-      <c r="C81" s="125" t="s">
-        <v>378</v>
+      <c r="C81" s="146" t="s">
+        <v>377</v>
       </c>
       <c r="D81" s="120"/>
       <c r="E81" s="120"/>
@@ -6105,28 +6114,28 @@
         <v>94</v>
       </c>
       <c r="G82" s="99" t="s">
+        <v>378</v>
+      </c>
+      <c r="H82" s="99" t="s">
         <v>379</v>
       </c>
-      <c r="H82" s="99" t="s">
+      <c r="I82" s="33" t="s">
         <v>380</v>
       </c>
-      <c r="I82" s="33" t="s">
+      <c r="J82" s="77" t="s">
         <v>381</v>
       </c>
-      <c r="J82" s="77" t="s">
+      <c r="K82" s="33" t="s">
         <v>382</v>
       </c>
-      <c r="K82" s="33" t="s">
+      <c r="L82" s="33" t="s">
         <v>383</v>
       </c>
-      <c r="L82" s="33" t="s">
-        <v>384</v>
-      </c>
       <c r="M82" s="33" t="s">
         <v>72</v>
       </c>
       <c r="N82" s="33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O82" s="77"/>
     </row>
@@ -6135,7 +6144,7 @@
         <v>92</v>
       </c>
       <c r="B83" s="64" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C83" s="26" t="s">
         <v>59</v>
@@ -6146,10 +6155,10 @@
         <v>94</v>
       </c>
       <c r="G83" s="99" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H83" s="99" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I83" s="33" t="s">
         <v>137</v>
@@ -6158,16 +6167,16 @@
         <v>83</v>
       </c>
       <c r="K83" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="L83" s="33" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M83" s="33" t="s">
         <v>72</v>
       </c>
       <c r="N83" s="33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O83" s="77"/>
     </row>
@@ -6187,28 +6196,28 @@
         <v>94</v>
       </c>
       <c r="G84" s="99" t="s">
+        <v>389</v>
+      </c>
+      <c r="H84" s="99" t="s">
+        <v>379</v>
+      </c>
+      <c r="I84" s="33" t="s">
+        <v>380</v>
+      </c>
+      <c r="J84" s="77" t="s">
+        <v>381</v>
+      </c>
+      <c r="K84" s="33" t="s">
         <v>390</v>
       </c>
-      <c r="H84" s="99" t="s">
-        <v>380</v>
-      </c>
-      <c r="I84" s="33" t="s">
-        <v>381</v>
-      </c>
-      <c r="J84" s="77" t="s">
-        <v>382</v>
-      </c>
-      <c r="K84" s="33" t="s">
-        <v>391</v>
-      </c>
       <c r="L84" s="33" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M84" s="33" t="s">
         <v>72</v>
       </c>
       <c r="N84" s="33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O84" s="77"/>
     </row>
@@ -6228,10 +6237,10 @@
         <v>94</v>
       </c>
       <c r="G85" s="100" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H85" s="100" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I85" s="33" t="s">
         <v>82</v>
@@ -6240,16 +6249,16 @@
         <v>83</v>
       </c>
       <c r="K85" s="33" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L85" s="33" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M85" s="33" t="s">
         <v>72</v>
       </c>
       <c r="N85" s="33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O85" s="77"/>
     </row>
@@ -6269,10 +6278,10 @@
         <v>94</v>
       </c>
       <c r="G86" s="100" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H86" s="100" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I86" s="33" t="s">
         <v>128</v>
@@ -6281,16 +6290,16 @@
         <v>83</v>
       </c>
       <c r="K86" s="33" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L86" s="33" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M86" s="33" t="s">
         <v>72</v>
       </c>
       <c r="N86" s="33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O86" s="77"/>
     </row>
@@ -6299,7 +6308,7 @@
         <v>92</v>
       </c>
       <c r="B87" s="64" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C87" s="26" t="s">
         <v>59</v>
@@ -6307,40 +6316,40 @@
       <c r="D87" s="27"/>
       <c r="E87" s="27"/>
       <c r="F87" s="99" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G87" s="99" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H87" s="99" t="s">
+        <v>403</v>
+      </c>
+      <c r="I87" s="33" t="s">
+        <v>380</v>
+      </c>
+      <c r="J87" s="77" t="s">
+        <v>381</v>
+      </c>
+      <c r="K87" s="33" t="s">
         <v>404</v>
       </c>
-      <c r="I87" s="33" t="s">
-        <v>381</v>
-      </c>
-      <c r="J87" s="77" t="s">
-        <v>382</v>
-      </c>
-      <c r="K87" s="33" t="s">
-        <v>405</v>
-      </c>
       <c r="L87" s="33" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M87" s="33" t="s">
         <v>72</v>
       </c>
       <c r="N87" s="33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O87" s="77"/>
     </row>
     <row r="88" spans="1:15" ht="31">
       <c r="A88" s="37" t="s">
+        <v>405</v>
+      </c>
+      <c r="B88" s="101" t="s">
         <v>406</v>
-      </c>
-      <c r="B88" s="101" t="s">
-        <v>407</v>
       </c>
       <c r="C88" s="26" t="s">
         <v>59</v>
@@ -6348,13 +6357,13 @@
       <c r="D88" s="27"/>
       <c r="E88" s="27"/>
       <c r="F88" s="100" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G88" s="100" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H88" s="100" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I88" s="33" t="s">
         <v>137</v>
@@ -6363,16 +6372,16 @@
         <v>83</v>
       </c>
       <c r="K88" s="33" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="L88" s="33" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M88" s="33" t="s">
         <v>72</v>
       </c>
       <c r="N88" s="33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O88" s="77"/>
     </row>
@@ -6381,7 +6390,7 @@
         <v>92</v>
       </c>
       <c r="B89" s="64" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C89" s="26" t="s">
         <v>59</v>
@@ -6389,40 +6398,40 @@
       <c r="D89" s="27"/>
       <c r="E89" s="27"/>
       <c r="F89" s="99" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G89" s="99" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H89" s="99" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I89" s="33" t="s">
+        <v>380</v>
+      </c>
+      <c r="J89" s="77" t="s">
         <v>381</v>
       </c>
-      <c r="J89" s="77" t="s">
-        <v>382</v>
-      </c>
       <c r="K89" s="33" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L89" s="33" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M89" s="33" t="s">
         <v>72</v>
       </c>
       <c r="N89" s="33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O89" s="77"/>
     </row>
     <row r="90" spans="1:15" ht="31">
       <c r="A90" s="37" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B90" s="101" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C90" s="26" t="s">
         <v>59</v>
@@ -6430,13 +6439,13 @@
       <c r="D90" s="27"/>
       <c r="E90" s="27"/>
       <c r="F90" s="100" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G90" s="100" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H90" s="100" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I90" s="33" t="s">
         <v>82</v>
@@ -6445,16 +6454,16 @@
         <v>83</v>
       </c>
       <c r="K90" s="33" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L90" s="33" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M90" s="33" t="s">
         <v>72</v>
       </c>
       <c r="N90" s="33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O90" s="77"/>
     </row>
@@ -6463,7 +6472,7 @@
         <v>92</v>
       </c>
       <c r="B91" s="64" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C91" s="26" t="s">
         <v>59</v>
@@ -6471,31 +6480,31 @@
       <c r="D91" s="58"/>
       <c r="E91" s="58"/>
       <c r="F91" s="99" t="s">
+        <v>415</v>
+      </c>
+      <c r="G91" s="99" t="s">
+        <v>378</v>
+      </c>
+      <c r="H91" s="99" t="s">
         <v>416</v>
       </c>
-      <c r="G91" s="99" t="s">
-        <v>379</v>
-      </c>
-      <c r="H91" s="99" t="s">
+      <c r="I91" s="33" t="s">
+        <v>380</v>
+      </c>
+      <c r="J91" s="77" t="s">
         <v>417</v>
       </c>
-      <c r="I91" s="33" t="s">
-        <v>381</v>
-      </c>
-      <c r="J91" s="77" t="s">
-        <v>418</v>
-      </c>
       <c r="K91" s="33" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="L91" s="33" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M91" s="33" t="s">
         <v>72</v>
       </c>
       <c r="N91" s="33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O91" s="77"/>
     </row>
@@ -6504,7 +6513,7 @@
         <v>92</v>
       </c>
       <c r="B92" s="64" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C92" s="26" t="s">
         <v>59</v>
@@ -6512,31 +6521,31 @@
       <c r="D92" s="58"/>
       <c r="E92" s="58"/>
       <c r="F92" s="99" t="s">
+        <v>415</v>
+      </c>
+      <c r="G92" s="99" t="s">
+        <v>388</v>
+      </c>
+      <c r="H92" s="99" t="s">
         <v>416</v>
       </c>
-      <c r="G92" s="99" t="s">
-        <v>389</v>
-      </c>
-      <c r="H92" s="99" t="s">
+      <c r="I92" s="33" t="s">
+        <v>380</v>
+      </c>
+      <c r="J92" s="77" t="s">
         <v>417</v>
       </c>
-      <c r="I92" s="33" t="s">
-        <v>381</v>
-      </c>
-      <c r="J92" s="77" t="s">
-        <v>418</v>
-      </c>
       <c r="K92" s="33" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="L92" s="33" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M92" s="33" t="s">
         <v>72</v>
       </c>
       <c r="N92" s="33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O92" s="77"/>
     </row>
@@ -6545,7 +6554,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="104" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C93" s="105" t="s">
         <v>59</v>
@@ -6553,31 +6562,31 @@
       <c r="D93" s="106"/>
       <c r="E93" s="106"/>
       <c r="F93" s="107" t="s">
+        <v>415</v>
+      </c>
+      <c r="G93" s="107" t="s">
+        <v>393</v>
+      </c>
+      <c r="H93" s="107" t="s">
         <v>416</v>
       </c>
-      <c r="G93" s="107" t="s">
-        <v>394</v>
-      </c>
-      <c r="H93" s="107" t="s">
+      <c r="I93" s="108" t="s">
+        <v>380</v>
+      </c>
+      <c r="J93" s="109" t="s">
         <v>417</v>
       </c>
-      <c r="I93" s="108" t="s">
-        <v>381</v>
-      </c>
-      <c r="J93" s="109" t="s">
-        <v>418</v>
-      </c>
       <c r="K93" s="108" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="L93" s="108" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M93" s="108" t="s">
         <v>72</v>
       </c>
       <c r="N93" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O93" s="77"/>
     </row>
@@ -6630,43 +6639,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="12.5">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="127" t="s">
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
-      <c r="H1" s="129"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="128"/>
-      <c r="K1" s="128"/>
-      <c r="L1" s="128"/>
-      <c r="M1" s="128"/>
-      <c r="N1" s="142"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="130"/>
     </row>
     <row r="2" spans="1:14" ht="12.5">
-      <c r="A2" s="140"/>
+      <c r="A2" s="123"/>
       <c r="B2" s="120"/>
       <c r="C2" s="120"/>
       <c r="D2" s="120"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="131"/>
-      <c r="G2" s="131"/>
-      <c r="H2" s="132"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="128"/>
       <c r="I2" s="120"/>
       <c r="J2" s="120"/>
       <c r="K2" s="120"/>
       <c r="L2" s="120"/>
       <c r="M2" s="120"/>
-      <c r="N2" s="143"/>
+      <c r="N2" s="131"/>
     </row>
     <row r="3" spans="1:14" ht="15.5">
-      <c r="A3" s="140"/>
+      <c r="A3" s="123"/>
       <c r="B3" s="120"/>
       <c r="C3" s="120"/>
       <c r="D3" s="120"/>
@@ -6675,121 +6684,121 @@
       </c>
       <c r="F3" s="120"/>
       <c r="G3" s="120"/>
-      <c r="H3" s="121"/>
+      <c r="H3" s="134"/>
       <c r="I3" s="120"/>
       <c r="J3" s="120"/>
       <c r="K3" s="120"/>
       <c r="L3" s="120"/>
       <c r="M3" s="120"/>
-      <c r="N3" s="143"/>
+      <c r="N3" s="131"/>
     </row>
     <row r="4" spans="1:14" ht="15.5">
-      <c r="A4" s="140"/>
+      <c r="A4" s="123"/>
       <c r="B4" s="120"/>
       <c r="C4" s="120"/>
       <c r="D4" s="120"/>
-      <c r="E4" s="134" t="s">
+      <c r="E4" s="135" t="s">
         <v>10</v>
       </c>
       <c r="F4" s="120"/>
       <c r="G4" s="120"/>
-      <c r="H4" s="121"/>
+      <c r="H4" s="134"/>
       <c r="I4" s="120"/>
       <c r="J4" s="120"/>
       <c r="K4" s="120"/>
       <c r="L4" s="120"/>
       <c r="M4" s="120"/>
-      <c r="N4" s="143"/>
+      <c r="N4" s="131"/>
     </row>
     <row r="5" spans="1:14" ht="15.5">
-      <c r="A5" s="140"/>
+      <c r="A5" s="123"/>
       <c r="B5" s="120"/>
       <c r="C5" s="120"/>
       <c r="D5" s="120"/>
-      <c r="E5" s="135" t="s">
+      <c r="E5" s="136" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="120"/>
       <c r="G5" s="120"/>
-      <c r="H5" s="121"/>
+      <c r="H5" s="134"/>
       <c r="I5" s="120"/>
       <c r="J5" s="120"/>
       <c r="K5" s="120"/>
       <c r="L5" s="120"/>
       <c r="M5" s="120"/>
-      <c r="N5" s="143"/>
+      <c r="N5" s="131"/>
     </row>
     <row r="6" spans="1:14" ht="15.5">
-      <c r="A6" s="140"/>
+      <c r="A6" s="123"/>
       <c r="B6" s="120"/>
       <c r="C6" s="120"/>
       <c r="D6" s="120"/>
-      <c r="E6" s="136" t="s">
+      <c r="E6" s="137" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="131"/>
-      <c r="G6" s="131"/>
-      <c r="H6" s="132"/>
+      <c r="F6" s="125"/>
+      <c r="G6" s="125"/>
+      <c r="H6" s="128"/>
       <c r="I6" s="120"/>
       <c r="J6" s="120"/>
       <c r="K6" s="120"/>
       <c r="L6" s="120"/>
       <c r="M6" s="120"/>
-      <c r="N6" s="143"/>
+      <c r="N6" s="131"/>
     </row>
     <row r="7" spans="1:14" ht="15.5">
-      <c r="A7" s="140"/>
+      <c r="A7" s="123"/>
       <c r="B7" s="120"/>
       <c r="C7" s="120"/>
       <c r="D7" s="120"/>
-      <c r="E7" s="137" t="s">
+      <c r="E7" s="138" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="131"/>
-      <c r="G7" s="131"/>
-      <c r="H7" s="132"/>
+      <c r="F7" s="125"/>
+      <c r="G7" s="125"/>
+      <c r="H7" s="128"/>
       <c r="I7" s="120"/>
       <c r="J7" s="120"/>
       <c r="K7" s="120"/>
       <c r="L7" s="120"/>
       <c r="M7" s="120"/>
-      <c r="N7" s="143"/>
+      <c r="N7" s="131"/>
     </row>
     <row r="8" spans="1:14" ht="15.5">
-      <c r="A8" s="140"/>
+      <c r="A8" s="123"/>
       <c r="B8" s="120"/>
       <c r="C8" s="120"/>
       <c r="D8" s="120"/>
-      <c r="E8" s="119" t="s">
+      <c r="E8" s="139" t="s">
         <v>24</v>
       </c>
       <c r="F8" s="120"/>
       <c r="G8" s="120"/>
-      <c r="H8" s="121"/>
+      <c r="H8" s="134"/>
       <c r="I8" s="120"/>
       <c r="J8" s="120"/>
       <c r="K8" s="120"/>
       <c r="L8" s="120"/>
       <c r="M8" s="120"/>
-      <c r="N8" s="143"/>
+      <c r="N8" s="131"/>
     </row>
     <row r="9" spans="1:14" ht="66" customHeight="1">
-      <c r="A9" s="130"/>
-      <c r="B9" s="131"/>
-      <c r="C9" s="131"/>
-      <c r="D9" s="131"/>
-      <c r="E9" s="122" t="s">
+      <c r="A9" s="124"/>
+      <c r="B9" s="125"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="142" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="123"/>
-      <c r="G9" s="123"/>
-      <c r="H9" s="124"/>
-      <c r="I9" s="131"/>
-      <c r="J9" s="131"/>
-      <c r="K9" s="131"/>
-      <c r="L9" s="131"/>
-      <c r="M9" s="131"/>
-      <c r="N9" s="144"/>
+      <c r="F9" s="143"/>
+      <c r="G9" s="143"/>
+      <c r="H9" s="144"/>
+      <c r="I9" s="125"/>
+      <c r="J9" s="125"/>
+      <c r="K9" s="125"/>
+      <c r="L9" s="125"/>
+      <c r="M9" s="125"/>
+      <c r="N9" s="132"/>
     </row>
     <row r="10" spans="1:14" ht="15.5">
       <c r="A10" s="15"/>
@@ -6821,12 +6830,12 @@
     </row>
     <row r="11" spans="1:14" ht="13.5">
       <c r="A11" s="20"/>
-      <c r="B11" s="145" t="s">
+      <c r="B11" s="140" t="s">
         <v>51</v>
       </c>
       <c r="C11" s="120"/>
       <c r="D11" s="120"/>
-      <c r="E11" s="147"/>
+      <c r="E11" s="145"/>
       <c r="F11" s="120"/>
       <c r="G11" s="120"/>
       <c r="H11" s="120"/>
@@ -6963,12 +6972,12 @@
     </row>
     <row r="16" spans="1:14" ht="13.5">
       <c r="A16" s="20"/>
-      <c r="B16" s="145" t="s">
+      <c r="B16" s="140" t="s">
         <v>98</v>
       </c>
       <c r="C16" s="120"/>
       <c r="D16" s="120"/>
-      <c r="E16" s="147"/>
+      <c r="E16" s="145"/>
       <c r="F16" s="120"/>
       <c r="G16" s="120"/>
       <c r="H16" s="120"/>
@@ -6981,7 +6990,7 @@
     </row>
     <row r="17" spans="1:15" ht="12.5">
       <c r="A17" s="48"/>
-      <c r="B17" s="146"/>
+      <c r="B17" s="141"/>
       <c r="C17" s="120"/>
       <c r="D17" s="120"/>
       <c r="E17" s="48"/>
@@ -7037,7 +7046,7 @@
         <v>54</v>
       </c>
       <c r="O18" s="18" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="16" thickTop="1">
@@ -7348,7 +7357,7 @@
         <v>1411</v>
       </c>
       <c r="O26" s="63" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="15.5">
@@ -7389,7 +7398,7 @@
         <v>134</v>
       </c>
       <c r="O27" s="63" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="15.5">
@@ -7430,7 +7439,7 @@
         <v>134</v>
       </c>
       <c r="O28" s="63" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="15.5">
@@ -7753,16 +7762,16 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="31">
+    <row r="37" spans="1:15" ht="15.5">
       <c r="A37" s="24" t="s">
         <v>74</v>
       </c>
       <c r="B37" s="68" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="C37" s="68"/>
       <c r="D37" s="68" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E37" s="75" t="s">
         <v>123</v>
@@ -7795,7 +7804,7 @@
         <v>1422</v>
       </c>
       <c r="O37" s="63" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="15.5">
@@ -7803,7 +7812,7 @@
         <v>74</v>
       </c>
       <c r="B38" s="68" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C38" s="68"/>
       <c r="D38" s="68"/>
@@ -7838,7 +7847,7 @@
         <v>1422</v>
       </c>
       <c r="O38" s="63" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="15.5">
@@ -7849,13 +7858,13 @@
       <c r="C39" s="68"/>
       <c r="D39" s="68"/>
       <c r="E39" s="75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F39" s="75">
         <v>1</v>
       </c>
       <c r="G39" s="75" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H39" s="63" t="s">
         <v>128</v>
@@ -7864,16 +7873,16 @@
         <v>143</v>
       </c>
       <c r="J39" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="K39" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="L39" s="63" t="s">
+        <v>72</v>
+      </c>
+      <c r="M39" s="63" t="s">
         <v>177</v>
-      </c>
-      <c r="K39" s="63" t="s">
-        <v>71</v>
-      </c>
-      <c r="L39" s="63" t="s">
-        <v>72</v>
-      </c>
-      <c r="M39" s="63" t="s">
-        <v>178</v>
       </c>
       <c r="N39" s="63"/>
     </row>
@@ -7885,13 +7894,13 @@
       <c r="C40" s="68"/>
       <c r="D40" s="68"/>
       <c r="E40" s="75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F40" s="75">
         <v>2</v>
       </c>
       <c r="G40" s="75" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H40" s="63" t="s">
         <v>128</v>
@@ -7900,16 +7909,16 @@
         <v>83</v>
       </c>
       <c r="J40" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="K40" s="76" t="s">
+        <v>181</v>
+      </c>
+      <c r="L40" s="63" t="s">
+        <v>72</v>
+      </c>
+      <c r="M40" s="63" t="s">
         <v>177</v>
-      </c>
-      <c r="K40" s="76" t="s">
-        <v>182</v>
-      </c>
-      <c r="L40" s="63" t="s">
-        <v>72</v>
-      </c>
-      <c r="M40" s="63" t="s">
-        <v>178</v>
       </c>
       <c r="N40" s="63"/>
     </row>
@@ -7921,13 +7930,13 @@
       <c r="C41" s="68"/>
       <c r="D41" s="68"/>
       <c r="E41" s="75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F41" s="75">
         <v>3</v>
       </c>
       <c r="G41" s="75" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H41" s="63" t="s">
         <v>68</v>
@@ -7936,7 +7945,7 @@
         <v>69</v>
       </c>
       <c r="J41" s="63" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K41" s="63" t="s">
         <v>71</v>
@@ -7960,7 +7969,7 @@
       </c>
       <c r="C42" s="68"/>
       <c r="D42" s="68" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E42" s="75" t="s">
         <v>132</v>
@@ -8079,10 +8088,10 @@
         <v>156</v>
       </c>
       <c r="C45" s="68" t="s">
+        <v>191</v>
+      </c>
+      <c r="D45" s="68" t="s">
         <v>192</v>
-      </c>
-      <c r="D45" s="68" t="s">
-        <v>193</v>
       </c>
       <c r="E45" s="75" t="s">
         <v>152</v>
@@ -8124,7 +8133,7 @@
       </c>
       <c r="C46" s="68"/>
       <c r="D46" s="68" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E46" s="75" t="s">
         <v>152</v>
@@ -8162,13 +8171,13 @@
         <v>74</v>
       </c>
       <c r="B47" s="68" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C47" s="68" t="s">
         <v>15</v>
       </c>
       <c r="D47" s="68" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E47" s="75" t="s">
         <v>78</v>
@@ -8206,27 +8215,27 @@
         <v>74</v>
       </c>
       <c r="B48" s="68" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C48" s="68"/>
       <c r="D48" s="68"/>
       <c r="E48" s="75" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F48" s="75">
         <v>1</v>
       </c>
       <c r="G48" s="75" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H48" s="63" t="s">
         <v>100</v>
       </c>
       <c r="I48" s="63" t="s">
+        <v>171</v>
+      </c>
+      <c r="J48" s="63" t="s">
         <v>172</v>
-      </c>
-      <c r="J48" s="63" t="s">
-        <v>173</v>
       </c>
       <c r="K48" s="63" t="s">
         <v>71</v>
@@ -8249,13 +8258,13 @@
       <c r="C49" s="68"/>
       <c r="D49" s="68"/>
       <c r="E49" s="75" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F49" s="75">
         <v>1</v>
       </c>
       <c r="G49" s="75" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H49" s="63" t="s">
         <v>68</v>
@@ -8264,7 +8273,7 @@
         <v>101</v>
       </c>
       <c r="J49" s="63" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K49" s="63" t="s">
         <v>71</v>
@@ -8284,22 +8293,22 @@
         <v>74</v>
       </c>
       <c r="B50" s="68" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C50" s="68" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D50" s="68" t="s">
         <v>15</v>
       </c>
       <c r="E50" s="75" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F50" s="75">
         <v>1</v>
       </c>
       <c r="G50" s="75" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H50" s="63" t="s">
         <v>68</v>
@@ -8308,7 +8317,7 @@
         <v>105</v>
       </c>
       <c r="J50" s="63" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K50" s="63" t="s">
         <v>71</v>
@@ -8328,20 +8337,20 @@
         <v>74</v>
       </c>
       <c r="B51" s="68" t="s">
+        <v>212</v>
+      </c>
+      <c r="C51" s="68" t="s">
         <v>213</v>
-      </c>
-      <c r="C51" s="68" t="s">
-        <v>214</v>
       </c>
       <c r="D51" s="68"/>
       <c r="E51" s="75" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F51" s="75">
         <v>1</v>
       </c>
       <c r="G51" s="75" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H51" s="63" t="s">
         <v>100</v>
@@ -8350,7 +8359,7 @@
         <v>111</v>
       </c>
       <c r="J51" s="63" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K51" s="63" t="s">
         <v>71</v>
@@ -8370,22 +8379,22 @@
         <v>57</v>
       </c>
       <c r="B52" s="72" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C52" s="72" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D52" s="72" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E52" s="74" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F52" s="74">
         <v>1</v>
       </c>
       <c r="G52" s="74" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H52" s="63" t="s">
         <v>100</v>
@@ -8394,7 +8403,7 @@
         <v>105</v>
       </c>
       <c r="J52" s="63" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K52" s="63" t="s">
         <v>71</v>
@@ -8415,26 +8424,26 @@
       </c>
       <c r="B53" s="56"/>
       <c r="C53" s="56" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D53" s="56"/>
       <c r="E53" s="71" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F53" s="71">
         <v>1</v>
       </c>
       <c r="G53" s="71" t="s">
+        <v>224</v>
+      </c>
+      <c r="H53" s="63" t="s">
+        <v>207</v>
+      </c>
+      <c r="I53" s="63" t="s">
         <v>225</v>
       </c>
-      <c r="H53" s="63" t="s">
-        <v>208</v>
-      </c>
-      <c r="I53" s="63" t="s">
+      <c r="J53" s="63" t="s">
         <v>226</v>
-      </c>
-      <c r="J53" s="63" t="s">
-        <v>227</v>
       </c>
       <c r="K53" s="63" t="s">
         <v>71</v>
@@ -8449,7 +8458,7 @@
         <v>1501</v>
       </c>
       <c r="O53" s="63" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="15.5">
@@ -8459,16 +8468,16 @@
       <c r="B54" s="56"/>
       <c r="C54" s="56"/>
       <c r="D54" s="56" t="s">
+        <v>220</v>
+      </c>
+      <c r="E54" s="71" t="s">
         <v>221</v>
-      </c>
-      <c r="E54" s="71" t="s">
-        <v>222</v>
       </c>
       <c r="F54" s="71" t="s">
         <v>136</v>
       </c>
       <c r="G54" s="71" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H54" s="63" t="s">
         <v>82</v>
@@ -8477,7 +8486,7 @@
         <v>143</v>
       </c>
       <c r="J54" s="63" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K54" s="63" t="s">
         <v>71</v>
@@ -8492,7 +8501,7 @@
         <v>3570</v>
       </c>
       <c r="O54" s="63" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="15.5">
@@ -8502,25 +8511,25 @@
       <c r="B55" s="56"/>
       <c r="C55" s="56"/>
       <c r="D55" s="56" t="s">
+        <v>220</v>
+      </c>
+      <c r="E55" s="71" t="s">
         <v>221</v>
-      </c>
-      <c r="E55" s="71" t="s">
-        <v>222</v>
       </c>
       <c r="F55" s="71" t="s">
         <v>141</v>
       </c>
       <c r="G55" s="71" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H55" s="63" t="s">
         <v>128</v>
       </c>
       <c r="I55" s="63" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J55" s="63" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K55" s="63" t="s">
         <v>71</v>
@@ -8535,7 +8544,7 @@
         <v>3570</v>
       </c>
       <c r="O55" s="63" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="15.5">
@@ -8543,31 +8552,31 @@
         <v>57</v>
       </c>
       <c r="B56" s="72" t="s">
+        <v>228</v>
+      </c>
+      <c r="C56" s="72" t="s">
+        <v>190</v>
+      </c>
+      <c r="D56" s="72" t="s">
         <v>229</v>
       </c>
-      <c r="C56" s="72" t="s">
-        <v>191</v>
-      </c>
-      <c r="D56" s="72" t="s">
-        <v>230</v>
-      </c>
       <c r="E56" s="74" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F56" s="74">
         <v>1</v>
       </c>
       <c r="G56" s="74" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H56" s="63" t="s">
         <v>100</v>
       </c>
       <c r="I56" s="63" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J56" s="63" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K56" s="63" t="s">
         <v>71</v>
@@ -8592,35 +8601,35 @@
       <c r="C57" s="68"/>
       <c r="D57" s="68"/>
       <c r="E57" s="75" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F57" s="75">
         <v>2</v>
       </c>
       <c r="G57" s="75" t="s">
+        <v>206</v>
+      </c>
+      <c r="H57" s="63" t="s">
         <v>207</v>
-      </c>
-      <c r="H57" s="63" t="s">
-        <v>208</v>
       </c>
       <c r="I57" s="63" t="s">
         <v>143</v>
       </c>
       <c r="J57" s="63" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K57" s="63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L57" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M57" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N57" s="63"/>
       <c r="O57" s="63" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="15.5">
@@ -8633,31 +8642,31 @@
       <c r="C58" s="79"/>
       <c r="D58" s="79"/>
       <c r="E58" s="80" t="s">
+        <v>205</v>
+      </c>
+      <c r="F58" s="80" t="s">
+        <v>234</v>
+      </c>
+      <c r="G58" s="80" t="s">
         <v>206</v>
-      </c>
-      <c r="F58" s="80" t="s">
-        <v>235</v>
-      </c>
-      <c r="G58" s="80" t="s">
-        <v>207</v>
       </c>
       <c r="H58" s="81" t="s">
         <v>137</v>
       </c>
       <c r="I58" s="81" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J58" s="81" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K58" s="81" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L58" s="81" t="s">
         <v>72</v>
       </c>
       <c r="M58" s="81" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N58" s="81"/>
     </row>
@@ -8673,35 +8682,35 @@
       </c>
       <c r="D59" s="68"/>
       <c r="E59" s="75" t="s">
+        <v>205</v>
+      </c>
+      <c r="F59" s="75" t="s">
+        <v>214</v>
+      </c>
+      <c r="G59" s="75" t="s">
         <v>206</v>
-      </c>
-      <c r="F59" s="75" t="s">
-        <v>215</v>
-      </c>
-      <c r="G59" s="75" t="s">
-        <v>207</v>
       </c>
       <c r="H59" s="63" t="s">
         <v>128</v>
       </c>
       <c r="I59" s="63" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J59" s="63" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K59" s="63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L59" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M59" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N59" s="63"/>
       <c r="O59" s="63" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="15.5">
@@ -8711,25 +8720,25 @@
       <c r="B60" s="68"/>
       <c r="C60" s="68"/>
       <c r="D60" s="68" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E60" s="75" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F60" s="75">
         <v>1</v>
       </c>
       <c r="G60" s="75" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H60" s="63" t="s">
         <v>137</v>
       </c>
       <c r="I60" s="63" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J60" s="63" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K60" s="63" t="s">
         <v>71</v>
@@ -8744,7 +8753,7 @@
         <v>1411</v>
       </c>
       <c r="O60" s="63" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="31">
@@ -8753,28 +8762,28 @@
       </c>
       <c r="B61" s="68"/>
       <c r="C61" s="68" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D61" s="68" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E61" s="75" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F61" s="75" t="s">
         <v>136</v>
       </c>
       <c r="G61" s="75" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H61" s="63" t="s">
         <v>82</v>
       </c>
       <c r="I61" s="63" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J61" s="63" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K61" s="63" t="s">
         <v>71</v>
@@ -8789,7 +8798,7 @@
         <v>3540</v>
       </c>
       <c r="O61" s="63" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="15.5">
@@ -8800,22 +8809,22 @@
       <c r="C62" s="68"/>
       <c r="D62" s="68"/>
       <c r="E62" s="75" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F62" s="75" t="s">
         <v>141</v>
       </c>
       <c r="G62" s="75" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H62" s="63" t="s">
         <v>82</v>
       </c>
       <c r="I62" s="63" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J62" s="63" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K62" s="63" t="s">
         <v>71</v>
@@ -8830,7 +8839,7 @@
         <v>3540</v>
       </c>
       <c r="O62" s="63" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="15.5">
@@ -8838,29 +8847,29 @@
         <v>74</v>
       </c>
       <c r="B63" s="68" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C63" s="68" t="s">
         <v>29</v>
       </c>
       <c r="D63" s="68"/>
       <c r="E63" s="75" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F63" s="75">
         <v>1</v>
       </c>
       <c r="G63" s="75" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H63" s="63" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I63" s="63" t="s">
+        <v>222</v>
+      </c>
+      <c r="J63" s="63" t="s">
         <v>223</v>
-      </c>
-      <c r="J63" s="63" t="s">
-        <v>224</v>
       </c>
       <c r="K63" s="63" t="s">
         <v>71</v>
@@ -8875,7 +8884,7 @@
         <v>1462</v>
       </c>
       <c r="O63" s="63" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="15.5">
@@ -8883,29 +8892,29 @@
         <v>74</v>
       </c>
       <c r="B64" s="68" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C64" s="68" t="s">
         <v>29</v>
       </c>
       <c r="D64" s="68"/>
       <c r="E64" s="75" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F64" s="75" t="s">
         <v>136</v>
       </c>
       <c r="G64" s="75" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H64" s="63" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I64" s="63" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J64" s="63" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K64" s="63" t="s">
         <v>71</v>
@@ -8920,7 +8929,7 @@
         <v>1232</v>
       </c>
       <c r="O64" s="63" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="15.5">
@@ -8928,18 +8937,18 @@
         <v>74</v>
       </c>
       <c r="B65" s="68" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C65" s="68"/>
       <c r="D65" s="68"/>
       <c r="E65" s="75" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F65" s="75" t="s">
         <v>141</v>
       </c>
       <c r="G65" s="75" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H65" s="63" t="s">
         <v>82</v>
@@ -8948,7 +8957,7 @@
         <v>143</v>
       </c>
       <c r="J65" s="63" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K65" s="63" t="s">
         <v>71</v>
@@ -8963,7 +8972,7 @@
         <v>1232</v>
       </c>
       <c r="O65" s="63" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="15.5">
@@ -8974,26 +8983,26 @@
         <v>29</v>
       </c>
       <c r="C66" s="56" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D66" s="56"/>
       <c r="E66" s="71" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F66" s="71">
         <v>1</v>
       </c>
       <c r="G66" s="71" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H66" s="63" t="s">
         <v>137</v>
       </c>
       <c r="I66" s="63" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J66" s="63" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K66" s="63" t="s">
         <v>71</v>
@@ -9008,7 +9017,7 @@
         <v>2550</v>
       </c>
       <c r="O66" s="63" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="67" spans="1:15" ht="15.5">
@@ -9021,22 +9030,22 @@
       <c r="C67" s="56"/>
       <c r="D67" s="56"/>
       <c r="E67" s="71" t="s">
+        <v>256</v>
+      </c>
+      <c r="F67" s="71" t="s">
+        <v>234</v>
+      </c>
+      <c r="G67" s="71" t="s">
         <v>257</v>
       </c>
-      <c r="F67" s="71" t="s">
-        <v>235</v>
-      </c>
-      <c r="G67" s="71" t="s">
-        <v>258</v>
-      </c>
       <c r="H67" s="83" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I67" s="63" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J67" s="63" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K67" s="63" t="s">
         <v>71</v>
@@ -9051,7 +9060,7 @@
         <v>3540</v>
       </c>
       <c r="O67" s="63" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="68" spans="1:15" ht="15.5">
@@ -9062,26 +9071,26 @@
         <v>29</v>
       </c>
       <c r="C68" s="85" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D68" s="85"/>
       <c r="E68" s="86" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F68" s="86" t="s">
         <v>141</v>
       </c>
       <c r="G68" s="86" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H68" s="87" t="s">
         <v>128</v>
       </c>
       <c r="I68" s="87" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J68" s="87" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K68" s="87" t="s">
         <v>71</v>
@@ -9104,19 +9113,19 @@
         <v>6</v>
       </c>
       <c r="C69" s="72" t="s">
+        <v>230</v>
+      </c>
+      <c r="D69" s="72" t="s">
+        <v>196</v>
+      </c>
+      <c r="E69" s="74" t="s">
         <v>231</v>
-      </c>
-      <c r="D69" s="72" t="s">
-        <v>197</v>
-      </c>
-      <c r="E69" s="74" t="s">
-        <v>232</v>
       </c>
       <c r="F69" s="74">
         <v>1</v>
       </c>
       <c r="G69" s="74" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H69" s="63" t="s">
         <v>68</v>
@@ -9125,7 +9134,7 @@
         <v>142</v>
       </c>
       <c r="J69" s="63" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K69" s="63" t="s">
         <v>71</v>
@@ -9145,20 +9154,20 @@
         <v>57</v>
       </c>
       <c r="B70" s="88" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C70" s="72"/>
       <c r="D70" s="72" t="s">
+        <v>230</v>
+      </c>
+      <c r="E70" s="74" t="s">
         <v>231</v>
-      </c>
-      <c r="E70" s="74" t="s">
-        <v>232</v>
       </c>
       <c r="F70" s="74">
         <v>2</v>
       </c>
       <c r="G70" s="74" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H70" s="63" t="s">
         <v>68</v>
@@ -9167,7 +9176,7 @@
         <v>69</v>
       </c>
       <c r="J70" s="63" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K70" s="63" t="s">
         <v>71</v>
@@ -9187,29 +9196,29 @@
         <v>74</v>
       </c>
       <c r="B71" s="68" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C71" s="68"/>
       <c r="D71" s="68" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E71" s="75" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F71" s="75">
         <v>1</v>
       </c>
       <c r="G71" s="75" t="s">
+        <v>237</v>
+      </c>
+      <c r="H71" s="63" t="s">
+        <v>207</v>
+      </c>
+      <c r="I71" s="63" t="s">
         <v>238</v>
       </c>
-      <c r="H71" s="63" t="s">
-        <v>208</v>
-      </c>
-      <c r="I71" s="63" t="s">
+      <c r="J71" s="63" t="s">
         <v>239</v>
-      </c>
-      <c r="J71" s="63" t="s">
-        <v>240</v>
       </c>
       <c r="K71" s="63" t="s">
         <v>71</v>
@@ -9230,26 +9239,26 @@
       </c>
       <c r="B72" s="68"/>
       <c r="C72" s="68" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D72" s="68"/>
       <c r="E72" s="75" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F72" s="75">
         <v>2</v>
       </c>
       <c r="G72" s="75" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H72" s="63" t="s">
         <v>137</v>
       </c>
       <c r="I72" s="63" t="s">
+        <v>238</v>
+      </c>
+      <c r="J72" s="63" t="s">
         <v>239</v>
-      </c>
-      <c r="J72" s="63" t="s">
-        <v>240</v>
       </c>
       <c r="K72" s="63" t="s">
         <v>71</v>
@@ -9272,13 +9281,13 @@
       <c r="C73" s="68"/>
       <c r="D73" s="68"/>
       <c r="E73" s="75" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F73" s="75">
         <v>1</v>
       </c>
       <c r="G73" s="75" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H73" s="63" t="s">
         <v>100</v>
@@ -9287,7 +9296,7 @@
         <v>69</v>
       </c>
       <c r="J73" s="63" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K73" s="63" t="s">
         <v>71</v>
@@ -9309,25 +9318,25 @@
       <c r="B74" s="72"/>
       <c r="C74" s="72"/>
       <c r="D74" s="72" t="s">
+        <v>284</v>
+      </c>
+      <c r="E74" s="74" t="s">
         <v>285</v>
-      </c>
-      <c r="E74" s="74" t="s">
-        <v>286</v>
       </c>
       <c r="F74" s="74">
         <v>1</v>
       </c>
       <c r="G74" s="74" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H74" s="63" t="s">
         <v>137</v>
       </c>
       <c r="I74" s="63" t="s">
+        <v>288</v>
+      </c>
+      <c r="J74" s="63" t="s">
         <v>289</v>
-      </c>
-      <c r="J74" s="63" t="s">
-        <v>290</v>
       </c>
       <c r="K74" s="63" t="s">
         <v>71</v>
@@ -9341,9 +9350,7 @@
       <c r="N74" s="63">
         <v>2432</v>
       </c>
-      <c r="O74" s="63" t="s">
-        <v>453</v>
-      </c>
+      <c r="O74" s="63"/>
     </row>
     <row r="75" spans="1:15" ht="15.5">
       <c r="A75" s="24" t="s">
@@ -9353,22 +9360,22 @@
       <c r="C75" s="72"/>
       <c r="D75" s="72"/>
       <c r="E75" s="74" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F75" s="74" t="s">
         <v>127</v>
       </c>
       <c r="G75" s="74" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H75" s="63" t="s">
         <v>128</v>
       </c>
       <c r="I75" s="63" t="s">
+        <v>288</v>
+      </c>
+      <c r="J75" s="63" t="s">
         <v>289</v>
-      </c>
-      <c r="J75" s="63" t="s">
-        <v>290</v>
       </c>
       <c r="K75" s="63" t="s">
         <v>71</v>
@@ -9382,9 +9389,7 @@
       <c r="N75" s="63">
         <v>2432</v>
       </c>
-      <c r="O75" s="63" t="s">
-        <v>453</v>
-      </c>
+      <c r="O75" s="63"/>
     </row>
     <row r="76" spans="1:15" ht="15.5">
       <c r="A76" s="24" t="s">
@@ -9395,25 +9400,25 @@
       </c>
       <c r="C76" s="72"/>
       <c r="D76" s="72" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E76" s="74" t="s">
+        <v>243</v>
+      </c>
+      <c r="F76" s="74" t="s">
         <v>244</v>
       </c>
-      <c r="F76" s="74" t="s">
+      <c r="G76" s="74" t="s">
         <v>245</v>
-      </c>
-      <c r="G76" s="74" t="s">
-        <v>246</v>
       </c>
       <c r="H76" s="63" t="s">
         <v>68</v>
       </c>
       <c r="I76" s="63" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J76" s="63" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K76" s="63" t="s">
         <v>71</v>
@@ -9433,31 +9438,31 @@
         <v>57</v>
       </c>
       <c r="B77" s="72" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C77" s="72" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D77" s="72" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E77" s="83" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F77" s="83" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G77" s="83" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H77" s="83" t="s">
         <v>100</v>
       </c>
       <c r="I77" s="83" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J77" s="63" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K77" s="63" t="s">
         <v>71</v>
@@ -9479,22 +9484,22 @@
       <c r="B78" s="72"/>
       <c r="C78" s="72"/>
       <c r="D78" s="72" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E78" s="74" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F78" s="74" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G78" s="74" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H78" s="63" t="s">
         <v>68</v>
       </c>
       <c r="I78" s="63" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J78" s="63" t="s">
         <v>70</v>
@@ -9518,28 +9523,28 @@
       </c>
       <c r="B79" s="72"/>
       <c r="C79" s="72" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D79" s="72" t="s">
         <v>146</v>
       </c>
       <c r="E79" s="74" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F79" s="74">
         <v>1</v>
       </c>
       <c r="G79" s="74" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H79" s="63" t="s">
         <v>68</v>
       </c>
       <c r="I79" s="63" t="s">
+        <v>262</v>
+      </c>
+      <c r="J79" s="63" t="s">
         <v>263</v>
-      </c>
-      <c r="J79" s="63" t="s">
-        <v>264</v>
       </c>
       <c r="K79" s="63" t="s">
         <v>71</v>
@@ -9560,28 +9565,28 @@
       </c>
       <c r="B80" s="72"/>
       <c r="C80" s="72" t="s">
+        <v>301</v>
+      </c>
+      <c r="D80" s="72" t="s">
         <v>302</v>
       </c>
-      <c r="D80" s="72" t="s">
-        <v>303</v>
-      </c>
       <c r="E80" s="74" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F80" s="74">
         <v>2</v>
       </c>
       <c r="G80" s="74" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H80" s="63" t="s">
         <v>100</v>
       </c>
       <c r="I80" s="63" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J80" s="63" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K80" s="63" t="s">
         <v>71</v>
@@ -9601,31 +9606,31 @@
         <v>57</v>
       </c>
       <c r="B81" s="72" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C81" s="72" t="s">
         <v>156</v>
       </c>
       <c r="D81" s="72" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E81" s="74" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F81" s="74">
         <v>3</v>
       </c>
       <c r="G81" s="74" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H81" s="63" t="s">
         <v>100</v>
       </c>
       <c r="I81" s="63" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J81" s="63" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K81" s="63" t="s">
         <v>71</v>
@@ -9647,25 +9652,25 @@
       <c r="B82" s="72"/>
       <c r="C82" s="72"/>
       <c r="D82" s="72" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E82" s="74" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F82" s="74">
         <v>1</v>
       </c>
       <c r="G82" s="74" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H82" s="63" t="s">
         <v>68</v>
       </c>
       <c r="I82" s="63" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J82" s="63" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K82" s="63" t="s">
         <v>71</v>
@@ -9685,31 +9690,31 @@
         <v>57</v>
       </c>
       <c r="B83" s="72" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C83" s="72" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D83" s="72" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E83" s="74" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F83" s="74">
         <v>2</v>
       </c>
       <c r="G83" s="74" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H83" s="63" t="s">
         <v>100</v>
       </c>
       <c r="I83" s="63" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J83" s="63" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K83" s="63" t="s">
         <v>71</v>
@@ -9729,31 +9734,31 @@
         <v>57</v>
       </c>
       <c r="B84" s="72" t="s">
+        <v>309</v>
+      </c>
+      <c r="C84" s="72" t="s">
         <v>310</v>
       </c>
-      <c r="C84" s="72" t="s">
+      <c r="D84" s="72" t="s">
         <v>311</v>
       </c>
-      <c r="D84" s="72" t="s">
-        <v>312</v>
-      </c>
       <c r="E84" s="74" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F84" s="74">
         <v>3</v>
       </c>
       <c r="G84" s="74" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H84" s="63" t="s">
         <v>100</v>
       </c>
       <c r="I84" s="63" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J84" s="63" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K84" s="63" t="s">
         <v>71</v>
@@ -9776,28 +9781,28 @@
         <v>146</v>
       </c>
       <c r="C85" s="72" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D85" s="72" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E85" s="74" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F85" s="74">
         <v>1</v>
       </c>
       <c r="G85" s="74" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H85" s="63" t="s">
         <v>100</v>
       </c>
       <c r="I85" s="63" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J85" s="63" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K85" s="63" t="s">
         <v>71</v>
@@ -9817,31 +9822,31 @@
         <v>57</v>
       </c>
       <c r="B86" s="72" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C86" s="72" t="s">
+        <v>319</v>
+      </c>
+      <c r="D86" s="72" t="s">
         <v>320</v>
       </c>
-      <c r="D86" s="72" t="s">
-        <v>321</v>
-      </c>
       <c r="E86" s="74" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F86" s="74">
         <v>1</v>
       </c>
       <c r="G86" s="74" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H86" s="63" t="s">
         <v>68</v>
       </c>
       <c r="I86" s="63" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J86" s="63" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K86" s="63" t="s">
         <v>71</v>
@@ -9861,31 +9866,31 @@
         <v>57</v>
       </c>
       <c r="B87" s="72" t="s">
+        <v>324</v>
+      </c>
+      <c r="C87" s="72" t="s">
         <v>325</v>
       </c>
-      <c r="C87" s="72" t="s">
-        <v>326</v>
-      </c>
       <c r="D87" s="72" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E87" s="74" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F87" s="74">
         <v>3</v>
       </c>
       <c r="G87" s="74" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H87" s="63" t="s">
         <v>68</v>
       </c>
       <c r="I87" s="63" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J87" s="63" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K87" s="63" t="s">
         <v>71</v>
@@ -9905,31 +9910,31 @@
         <v>57</v>
       </c>
       <c r="B88" s="96" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C88" s="96" t="s">
+        <v>332</v>
+      </c>
+      <c r="D88" s="96" t="s">
         <v>333</v>
       </c>
-      <c r="D88" s="96" t="s">
-        <v>334</v>
-      </c>
       <c r="E88" s="83" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F88" s="83">
         <v>4</v>
       </c>
       <c r="G88" s="83" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H88" s="83" t="s">
         <v>100</v>
       </c>
       <c r="I88" s="83" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J88" s="83" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K88" s="63" t="s">
         <v>71</v>
@@ -9949,31 +9954,31 @@
         <v>74</v>
       </c>
       <c r="B89" s="68" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C89" s="68" t="s">
         <v>20</v>
       </c>
       <c r="D89" s="68" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E89" s="75" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F89" s="75">
         <v>1</v>
       </c>
       <c r="G89" s="75" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H89" s="63" t="s">
         <v>100</v>
       </c>
       <c r="I89" s="63" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J89" s="63" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K89" s="63" t="s">
         <v>71</v>
@@ -9993,29 +9998,29 @@
         <v>74</v>
       </c>
       <c r="B90" s="68" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C90" s="68"/>
       <c r="D90" s="68" t="s">
         <v>6</v>
       </c>
       <c r="E90" s="75" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F90" s="75">
         <v>2</v>
       </c>
       <c r="G90" s="75" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H90" s="63" t="s">
         <v>100</v>
       </c>
       <c r="I90" s="63" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J90" s="63" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K90" s="63" t="s">
         <v>71</v>
@@ -10035,11 +10040,11 @@
         <v>57</v>
       </c>
       <c r="B91" s="72" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C91" s="72"/>
       <c r="D91" s="72" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E91" s="74" t="s">
         <v>62</v>
@@ -10048,7 +10053,7 @@
         <v>1</v>
       </c>
       <c r="G91" s="74" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H91" s="63" t="s">
         <v>100</v>
@@ -10057,7 +10062,7 @@
         <v>101</v>
       </c>
       <c r="J91" s="63" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K91" s="63" t="s">
         <v>71</v>
@@ -10077,7 +10082,7 @@
         <v>57</v>
       </c>
       <c r="B92" s="72" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C92" s="72" t="s">
         <v>6</v>
@@ -10090,7 +10095,7 @@
         <v>2</v>
       </c>
       <c r="G92" s="74" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H92" s="63" t="s">
         <v>100</v>
@@ -10099,7 +10104,7 @@
         <v>69</v>
       </c>
       <c r="J92" s="63" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K92" s="63" t="s">
         <v>71</v>
@@ -10120,19 +10125,19 @@
       </c>
       <c r="B93" s="72"/>
       <c r="C93" s="88" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D93" s="72" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E93" s="74" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F93" s="74">
         <v>1</v>
       </c>
       <c r="G93" s="74" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H93" s="63" t="s">
         <v>68</v>
@@ -10141,7 +10146,7 @@
         <v>142</v>
       </c>
       <c r="J93" s="63" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K93" s="63" t="s">
         <v>71</v>
@@ -10162,28 +10167,28 @@
       </c>
       <c r="B94" s="72"/>
       <c r="C94" s="72" t="s">
+        <v>346</v>
+      </c>
+      <c r="D94" s="72" t="s">
         <v>347</v>
       </c>
-      <c r="D94" s="72" t="s">
-        <v>348</v>
-      </c>
       <c r="E94" s="74" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F94" s="74">
         <v>2</v>
       </c>
       <c r="G94" s="74" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H94" s="63" t="s">
         <v>68</v>
       </c>
       <c r="I94" s="63" t="s">
+        <v>317</v>
+      </c>
+      <c r="J94" s="63" t="s">
         <v>318</v>
-      </c>
-      <c r="J94" s="63" t="s">
-        <v>319</v>
       </c>
       <c r="K94" s="63" t="s">
         <v>71</v>
@@ -10205,25 +10210,25 @@
       <c r="B95" s="72"/>
       <c r="C95" s="72"/>
       <c r="D95" s="72" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E95" s="74" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F95" s="74">
         <v>1</v>
       </c>
       <c r="G95" s="74" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H95" s="63" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I95" s="63" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J95" s="63" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K95" s="63" t="s">
         <v>71</v>
@@ -10243,31 +10248,31 @@
         <v>57</v>
       </c>
       <c r="B96" s="72" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C96" s="72" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D96" s="72" t="s">
         <v>159</v>
       </c>
       <c r="E96" s="74" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F96" s="74">
         <v>2</v>
       </c>
       <c r="G96" s="74" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H96" s="63" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I96" s="63" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J96" s="63" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K96" s="63" t="s">
         <v>71</v>
@@ -10288,19 +10293,19 @@
       </c>
       <c r="B97" s="68"/>
       <c r="C97" s="68" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D97" s="68" t="s">
         <v>29</v>
       </c>
       <c r="E97" s="75" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F97" s="75">
         <v>2</v>
       </c>
       <c r="G97" s="75" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H97" s="63" t="s">
         <v>68</v>
@@ -10309,7 +10314,7 @@
         <v>69</v>
       </c>
       <c r="J97" s="63" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="K97" s="63" t="s">
         <v>71</v>
@@ -10334,13 +10339,13 @@
         <v>29</v>
       </c>
       <c r="E98" s="75" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F98" s="75">
         <v>1</v>
       </c>
       <c r="G98" s="75" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H98" s="63" t="s">
         <v>68</v>
@@ -10349,7 +10354,7 @@
         <v>142</v>
       </c>
       <c r="J98" s="63" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="K98" s="63" t="s">
         <v>71</v>
@@ -10369,20 +10374,20 @@
         <v>74</v>
       </c>
       <c r="B99" s="68" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C99" s="68" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D99" s="68"/>
       <c r="E99" s="75" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F99" s="75">
         <v>1</v>
       </c>
       <c r="G99" s="75" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H99" s="63" t="s">
         <v>100</v>
@@ -10391,7 +10396,7 @@
         <v>111</v>
       </c>
       <c r="J99" s="63" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="K99" s="63" t="s">
         <v>71</v>
@@ -10411,22 +10416,22 @@
         <v>74</v>
       </c>
       <c r="B100" s="68" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C100" s="68" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D100" s="68" t="s">
         <v>20</v>
       </c>
       <c r="E100" s="75" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F100" s="75">
         <v>2</v>
       </c>
       <c r="G100" s="75" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H100" s="63" t="s">
         <v>68</v>
@@ -10435,7 +10440,7 @@
         <v>142</v>
       </c>
       <c r="J100" s="63" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K100" s="63" t="s">
         <v>71</v>
@@ -10457,16 +10462,16 @@
       <c r="B101" s="68"/>
       <c r="C101" s="68"/>
       <c r="D101" s="68" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E101" s="75" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F101" s="75">
         <v>1</v>
       </c>
       <c r="G101" s="75" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H101" s="63" t="s">
         <v>68</v>
@@ -10475,7 +10480,7 @@
         <v>111</v>
       </c>
       <c r="J101" s="63" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K101" s="63" t="s">
         <v>71</v>
@@ -10498,25 +10503,25 @@
       <c r="C102" s="56"/>
       <c r="D102" s="56"/>
       <c r="E102" s="71" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F102" s="71">
         <v>1</v>
       </c>
       <c r="G102" s="71" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H102" s="63" t="s">
         <v>82</v>
       </c>
       <c r="I102" s="63" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J102" s="63" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K102" s="76" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L102" s="63" t="s">
         <v>72</v>
@@ -10538,13 +10543,13 @@
         <v>20</v>
       </c>
       <c r="E103" s="71" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F103" s="71">
         <v>2</v>
       </c>
       <c r="G103" s="71" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H103" s="63" t="s">
         <v>82</v>
@@ -10553,7 +10558,7 @@
         <v>83</v>
       </c>
       <c r="J103" s="63" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="K103" s="63" t="s">
         <v>71</v>
@@ -10576,22 +10581,22 @@
       <c r="C104" s="56"/>
       <c r="D104" s="56"/>
       <c r="E104" s="71" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F104" s="71">
         <v>3</v>
       </c>
       <c r="G104" s="71" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H104" s="63" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I104" s="63" t="s">
         <v>83</v>
       </c>
       <c r="J104" s="63" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="K104" s="63" t="s">
         <v>71</v>
@@ -10611,18 +10616,18 @@
         <v>55</v>
       </c>
       <c r="B105" s="85" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C105" s="85"/>
       <c r="D105" s="85"/>
       <c r="E105" s="86" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F105" s="86">
         <v>2</v>
       </c>
       <c r="G105" s="86" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H105" s="87" t="s">
         <v>68</v>
@@ -10631,7 +10636,7 @@
         <v>101</v>
       </c>
       <c r="J105" s="87" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K105" s="87" t="s">
         <v>71</v>
@@ -10640,7 +10645,7 @@
         <v>72</v>
       </c>
       <c r="M105" s="87" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="N105" s="87"/>
     </row>
@@ -10652,13 +10657,13 @@
       <c r="C106" s="56"/>
       <c r="D106" s="56"/>
       <c r="E106" s="71" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F106" s="71">
         <v>1</v>
       </c>
       <c r="G106" s="71" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H106" s="63" t="s">
         <v>68</v>
@@ -10667,7 +10672,7 @@
         <v>69</v>
       </c>
       <c r="J106" s="63" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K106" s="63" t="s">
         <v>71</v>
@@ -10687,18 +10692,18 @@
         <v>55</v>
       </c>
       <c r="B107" s="56" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C107" s="56"/>
       <c r="D107" s="56"/>
       <c r="E107" s="71" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F107" s="71">
         <v>2</v>
       </c>
       <c r="G107" s="71" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H107" s="63" t="s">
         <v>100</v>
@@ -10707,7 +10712,7 @@
         <v>101</v>
       </c>
       <c r="J107" s="63" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K107" s="63" t="s">
         <v>71</v>
@@ -10730,17 +10735,17 @@
         <v>6</v>
       </c>
       <c r="C108" s="68" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D108" s="68"/>
       <c r="E108" s="75" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F108" s="75">
         <v>1</v>
       </c>
       <c r="G108" s="75" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H108" s="63" t="s">
         <v>100</v>
@@ -10749,7 +10754,7 @@
         <v>69</v>
       </c>
       <c r="J108" s="63" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K108" s="63" t="s">
         <v>71</v>
@@ -10770,26 +10775,26 @@
       </c>
       <c r="B109" s="68"/>
       <c r="C109" s="68" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D109" s="68"/>
       <c r="E109" s="75" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F109" s="75">
         <v>2</v>
       </c>
       <c r="G109" s="75" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H109" s="63" t="s">
         <v>68</v>
       </c>
       <c r="I109" s="63" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J109" s="63" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K109" s="63" t="s">
         <v>71</v>
@@ -10810,28 +10815,28 @@
       </c>
       <c r="B110" s="68"/>
       <c r="C110" s="68" t="s">
+        <v>394</v>
+      </c>
+      <c r="D110" s="68" t="s">
         <v>395</v>
       </c>
-      <c r="D110" s="68" t="s">
-        <v>396</v>
-      </c>
       <c r="E110" s="75" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F110" s="75">
         <v>1</v>
       </c>
       <c r="G110" s="75" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H110" s="63" t="s">
         <v>68</v>
       </c>
       <c r="I110" s="63" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J110" s="63" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="K110" s="63" t="s">
         <v>71</v>
@@ -10854,19 +10859,19 @@
         <v>146</v>
       </c>
       <c r="C111" s="68" t="s">
+        <v>397</v>
+      </c>
+      <c r="D111" s="68" t="s">
         <v>398</v>
       </c>
-      <c r="D111" s="68" t="s">
-        <v>399</v>
-      </c>
       <c r="E111" s="75" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F111" s="75">
         <v>1</v>
       </c>
       <c r="G111" s="75" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H111" s="63" t="s">
         <v>68</v>
@@ -10875,7 +10880,7 @@
         <v>69</v>
       </c>
       <c r="J111" s="63" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K111" s="63" t="s">
         <v>71</v>
@@ -10895,22 +10900,22 @@
         <v>74</v>
       </c>
       <c r="B112" s="68" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C112" s="68" t="s">
+        <v>401</v>
+      </c>
+      <c r="D112" s="68" t="s">
         <v>402</v>
       </c>
-      <c r="D112" s="68" t="s">
-        <v>403</v>
-      </c>
       <c r="E112" s="75" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F112" s="75">
         <v>1</v>
       </c>
       <c r="G112" s="75" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H112" s="63" t="s">
         <v>68</v>
@@ -10919,7 +10924,7 @@
         <v>142</v>
       </c>
       <c r="J112" s="63" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K112" s="63" t="s">
         <v>71</v>
@@ -10939,20 +10944,20 @@
         <v>74</v>
       </c>
       <c r="B113" s="68" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C113" s="68" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D113" s="68"/>
       <c r="E113" s="75" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F113" s="75">
         <v>1</v>
       </c>
       <c r="G113" s="75" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H113" s="63" t="s">
         <v>68</v>
@@ -10961,7 +10966,7 @@
         <v>69</v>
       </c>
       <c r="J113" s="63" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K113" s="63" t="s">
         <v>71</v>
@@ -10990,16 +10995,16 @@
         <v>1</v>
       </c>
       <c r="G114" s="71" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H114" s="63" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I114" s="63" t="s">
         <v>138</v>
       </c>
       <c r="J114" s="63" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K114" s="63" t="s">
         <v>71</v>
@@ -11014,7 +11019,7 @@
         <v>1411</v>
       </c>
       <c r="O114" s="63" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="115" spans="1:15" ht="15.5">
@@ -11031,16 +11036,16 @@
         <v>2</v>
       </c>
       <c r="G115" s="71" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H115" s="63" t="s">
         <v>137</v>
       </c>
       <c r="I115" s="63" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J115" s="63" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K115" s="63" t="s">
         <v>71</v>
@@ -11055,7 +11060,7 @@
         <v>1360</v>
       </c>
       <c r="O115" s="63" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="116" spans="1:15" ht="15.5">
@@ -11065,7 +11070,7 @@
       <c r="B116" s="102"/>
       <c r="C116" s="102"/>
       <c r="D116" s="102" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E116" s="103" t="s">
         <v>94</v>
@@ -11074,27 +11079,27 @@
         <v>3</v>
       </c>
       <c r="G116" s="103" t="s">
+        <v>379</v>
+      </c>
+      <c r="H116" s="63" t="s">
         <v>380</v>
-      </c>
-      <c r="H116" s="63" t="s">
-        <v>381</v>
       </c>
       <c r="I116" s="63"/>
       <c r="J116" s="63" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K116" s="63" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L116" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M116" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N116" s="63"/>
       <c r="O116" s="63" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="117" spans="1:15" ht="15.5">
@@ -11111,27 +11116,27 @@
         <v>4</v>
       </c>
       <c r="G117" s="103" t="s">
+        <v>379</v>
+      </c>
+      <c r="H117" s="63" t="s">
         <v>380</v>
-      </c>
-      <c r="H117" s="63" t="s">
-        <v>381</v>
       </c>
       <c r="I117" s="63"/>
       <c r="J117" s="63" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K117" s="63" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L117" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M117" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N117" s="63"/>
       <c r="O117" s="63" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="118" spans="1:15" ht="15.5">
@@ -11145,19 +11150,19 @@
         <v>94</v>
       </c>
       <c r="F118" s="71" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G118" s="71" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H118" s="63" t="s">
         <v>82</v>
       </c>
       <c r="I118" s="63" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J118" s="63" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K118" s="63" t="s">
         <v>71</v>
@@ -11172,7 +11177,7 @@
         <v>3314</v>
       </c>
       <c r="O118" s="63" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="119" spans="1:15" ht="15.5">
@@ -11186,19 +11191,19 @@
         <v>94</v>
       </c>
       <c r="F119" s="71" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G119" s="71" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H119" s="63" t="s">
         <v>82</v>
       </c>
       <c r="I119" s="63" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J119" s="63" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K119" s="63" t="s">
         <v>71</v>
@@ -11213,7 +11218,7 @@
         <v>3314</v>
       </c>
       <c r="O119" s="63" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="120" spans="1:15" ht="15.5">
@@ -11227,19 +11232,19 @@
         <v>94</v>
       </c>
       <c r="F120" s="71" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G120" s="71" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H120" s="63" t="s">
         <v>128</v>
       </c>
       <c r="I120" s="63" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J120" s="63" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K120" s="63" t="s">
         <v>71</v>
@@ -11254,7 +11259,7 @@
         <v>3314</v>
       </c>
       <c r="O120" s="63" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="121" spans="1:15" ht="15.5">
@@ -11268,19 +11273,19 @@
         <v>94</v>
       </c>
       <c r="F121" s="71" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G121" s="71" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H121" s="63" t="s">
         <v>128</v>
       </c>
       <c r="I121" s="63" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J121" s="63" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K121" s="63" t="s">
         <v>71</v>
@@ -11295,7 +11300,7 @@
         <v>3314</v>
       </c>
       <c r="O121" s="63" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="122" spans="1:15" ht="15.5">
@@ -11309,32 +11314,32 @@
         <v>94</v>
       </c>
       <c r="F122" s="71" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G122" s="71" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H122" s="63" t="s">
         <v>82</v>
       </c>
       <c r="I122" s="63" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J122" s="63" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K122" s="63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L122" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M122" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N122" s="63"/>
       <c r="O122" s="63" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="123" spans="1:15" ht="15.5">
@@ -11348,32 +11353,32 @@
         <v>94</v>
       </c>
       <c r="F123" s="71" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G123" s="71" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H123" s="63" t="s">
         <v>82</v>
       </c>
       <c r="I123" s="63" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J123" s="63" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K123" s="63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L123" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M123" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N123" s="63"/>
       <c r="O123" s="63" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="124" spans="1:15" ht="15.5">
@@ -11387,32 +11392,32 @@
         <v>94</v>
       </c>
       <c r="F124" s="71" t="s">
+        <v>424</v>
+      </c>
+      <c r="G124" s="71" t="s">
+        <v>379</v>
+      </c>
+      <c r="H124" s="63" t="s">
+        <v>265</v>
+      </c>
+      <c r="I124" s="63" t="s">
         <v>425</v>
       </c>
-      <c r="G124" s="71" t="s">
-        <v>380</v>
-      </c>
-      <c r="H124" s="63" t="s">
-        <v>266</v>
-      </c>
-      <c r="I124" s="63" t="s">
-        <v>426</v>
-      </c>
       <c r="J124" s="63" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K124" s="63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L124" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M124" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N124" s="63"/>
       <c r="O124" s="63" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="125" spans="1:15" ht="15.5">
@@ -11426,32 +11431,32 @@
         <v>94</v>
       </c>
       <c r="F125" s="71" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G125" s="71" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H125" s="63" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I125" s="63" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J125" s="63" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K125" s="63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L125" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M125" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N125" s="63"/>
       <c r="O125" s="63" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="126" spans="1:15" ht="15.5">
@@ -11462,22 +11467,22 @@
       <c r="C126" s="102"/>
       <c r="D126" s="102"/>
       <c r="E126" s="103" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F126" s="103">
         <v>1</v>
       </c>
       <c r="G126" s="103" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H126" s="63" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I126" s="63" t="s">
         <v>138</v>
       </c>
       <c r="J126" s="63" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K126" s="63" t="s">
         <v>71</v>
@@ -11492,7 +11497,7 @@
         <v>2515</v>
       </c>
       <c r="O126" s="63" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="127" spans="1:15" ht="15.5">
@@ -11503,33 +11508,33 @@
       <c r="C127" s="102"/>
       <c r="D127" s="102"/>
       <c r="E127" s="103" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F127" s="103">
         <v>2</v>
       </c>
       <c r="G127" s="103" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H127" s="63" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I127" s="63"/>
       <c r="J127" s="63" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="K127" s="63" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L127" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M127" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N127" s="63"/>
       <c r="O127" s="63" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="128" spans="1:15" ht="15.5">
@@ -11540,33 +11545,33 @@
       <c r="C128" s="102"/>
       <c r="D128" s="102"/>
       <c r="E128" s="103" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F128" s="103">
         <v>3</v>
       </c>
       <c r="G128" s="103" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H128" s="63" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I128" s="63"/>
       <c r="J128" s="63" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K128" s="63" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L128" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M128" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N128" s="63"/>
       <c r="O128" s="63" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="129" spans="1:15" ht="15.5">
@@ -11577,22 +11582,22 @@
       <c r="C129" s="56"/>
       <c r="D129" s="56"/>
       <c r="E129" s="71" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F129" s="71" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G129" s="71" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H129" s="63" t="s">
         <v>82</v>
       </c>
       <c r="I129" s="63" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J129" s="63" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K129" s="63" t="s">
         <v>71</v>
@@ -11607,7 +11612,7 @@
         <v>3344</v>
       </c>
       <c r="O129" s="63" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="130" spans="1:15" ht="15.5">
@@ -11618,22 +11623,22 @@
       <c r="C130" s="56"/>
       <c r="D130" s="56"/>
       <c r="E130" s="71" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F130" s="71" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G130" s="71" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H130" s="63" t="s">
         <v>82</v>
       </c>
       <c r="I130" s="63" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J130" s="63" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K130" s="63" t="s">
         <v>71</v>
@@ -11648,7 +11653,7 @@
         <v>3344</v>
       </c>
       <c r="O130" s="63" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="131" spans="1:15" ht="15.5">
@@ -11659,22 +11664,22 @@
       <c r="C131" s="56"/>
       <c r="D131" s="56"/>
       <c r="E131" s="71" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F131" s="71" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G131" s="71" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H131" s="63" t="s">
         <v>137</v>
       </c>
       <c r="I131" s="63" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J131" s="63" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="K131" s="63" t="s">
         <v>71</v>
@@ -11689,7 +11694,7 @@
         <v>3314</v>
       </c>
       <c r="O131" s="63" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="132" spans="1:15" ht="15.5">
@@ -11700,35 +11705,35 @@
       <c r="C132" s="56"/>
       <c r="D132" s="56"/>
       <c r="E132" s="71" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F132" s="71" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G132" s="71" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H132" s="63" t="s">
         <v>128</v>
       </c>
       <c r="I132" s="63" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J132" s="63" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K132" s="63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L132" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M132" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N132" s="63"/>
       <c r="O132" s="63" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="133" spans="1:15" ht="15.5">
@@ -11739,35 +11744,35 @@
       <c r="C133" s="56"/>
       <c r="D133" s="56"/>
       <c r="E133" s="71" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F133" s="71" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G133" s="71" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H133" s="63" t="s">
         <v>128</v>
       </c>
       <c r="I133" s="63" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J133" s="63" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K133" s="63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L133" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M133" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N133" s="63"/>
       <c r="O133" s="63" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="134" spans="1:15" ht="15.5">
@@ -11780,22 +11785,22 @@
         <v>17</v>
       </c>
       <c r="E134" s="71" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F134" s="71">
         <v>1</v>
       </c>
       <c r="G134" s="71" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H134" s="63" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I134" s="63" t="s">
         <v>138</v>
       </c>
       <c r="J134" s="63" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="K134" s="63" t="s">
         <v>71</v>
@@ -11810,7 +11815,7 @@
         <v>1501</v>
       </c>
       <c r="O134" s="63" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="135" spans="1:15" ht="15.5">
@@ -11820,25 +11825,25 @@
       <c r="B135" s="56"/>
       <c r="C135" s="56"/>
       <c r="D135" s="56" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E135" s="71" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F135" s="71">
         <v>2</v>
       </c>
       <c r="G135" s="71" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H135" s="63" t="s">
         <v>137</v>
       </c>
       <c r="I135" s="63" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J135" s="63" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K135" s="63" t="s">
         <v>71</v>
@@ -11853,7 +11858,7 @@
         <v>3332</v>
       </c>
       <c r="O135" s="63" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="136" spans="1:15" ht="15.5">
@@ -11864,33 +11869,33 @@
       <c r="C136" s="56"/>
       <c r="D136" s="56"/>
       <c r="E136" s="71" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F136" s="71">
         <v>3</v>
       </c>
       <c r="G136" s="71" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H136" s="63" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I136" s="63"/>
       <c r="J136" s="63" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K136" s="63" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L136" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M136" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N136" s="63"/>
       <c r="O136" s="63" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="137" spans="1:15" ht="15.5">
@@ -11901,33 +11906,33 @@
       <c r="C137" s="56"/>
       <c r="D137" s="56"/>
       <c r="E137" s="71" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F137" s="71">
         <v>4</v>
       </c>
       <c r="G137" s="71" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H137" s="63" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I137" s="63"/>
       <c r="J137" s="63" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K137" s="63" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L137" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M137" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N137" s="63"/>
       <c r="O137" s="63" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="138" spans="1:15" ht="15.5">
@@ -11940,22 +11945,22 @@
         <v>17</v>
       </c>
       <c r="E138" s="71" t="s">
+        <v>415</v>
+      </c>
+      <c r="F138" s="71" t="s">
+        <v>414</v>
+      </c>
+      <c r="G138" s="71" t="s">
         <v>416</v>
-      </c>
-      <c r="F138" s="71" t="s">
-        <v>415</v>
-      </c>
-      <c r="G138" s="71" t="s">
-        <v>417</v>
       </c>
       <c r="H138" s="63" t="s">
         <v>82</v>
       </c>
       <c r="I138" s="63" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J138" s="63" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="K138" s="63" t="s">
         <v>71</v>
@@ -11970,7 +11975,7 @@
         <v>3332</v>
       </c>
       <c r="O138" s="63" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="139" spans="1:15" ht="15.5">
@@ -11981,22 +11986,22 @@
       <c r="C139" s="56"/>
       <c r="D139" s="56"/>
       <c r="E139" s="71" t="s">
+        <v>415</v>
+      </c>
+      <c r="F139" s="71" t="s">
+        <v>418</v>
+      </c>
+      <c r="G139" s="71" t="s">
         <v>416</v>
-      </c>
-      <c r="F139" s="71" t="s">
-        <v>419</v>
-      </c>
-      <c r="G139" s="71" t="s">
-        <v>417</v>
       </c>
       <c r="H139" s="63" t="s">
         <v>82</v>
       </c>
       <c r="I139" s="63" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J139" s="63" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="K139" s="63" t="s">
         <v>71</v>
@@ -12011,7 +12016,7 @@
         <v>3332</v>
       </c>
       <c r="O139" s="63" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="140" spans="1:15" ht="31">
@@ -12020,26 +12025,26 @@
       </c>
       <c r="B140" s="56"/>
       <c r="C140" s="56" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D140" s="56"/>
       <c r="E140" s="71" t="s">
+        <v>415</v>
+      </c>
+      <c r="F140" s="71" t="s">
+        <v>419</v>
+      </c>
+      <c r="G140" s="71" t="s">
         <v>416</v>
-      </c>
-      <c r="F140" s="71" t="s">
-        <v>420</v>
-      </c>
-      <c r="G140" s="71" t="s">
-        <v>417</v>
       </c>
       <c r="H140" s="63" t="s">
         <v>128</v>
       </c>
       <c r="I140" s="63" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J140" s="63" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K140" s="63" t="s">
         <v>71</v>
@@ -12054,7 +12059,7 @@
         <v>3332</v>
       </c>
       <c r="O140" s="63" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="141" spans="1:15" ht="15.5">
@@ -12065,33 +12070,33 @@
       <c r="C141" s="56"/>
       <c r="D141" s="56"/>
       <c r="E141" s="71" t="s">
+        <v>415</v>
+      </c>
+      <c r="F141" s="71" t="s">
+        <v>420</v>
+      </c>
+      <c r="G141" s="71" t="s">
         <v>416</v>
       </c>
-      <c r="F141" s="71" t="s">
-        <v>421</v>
-      </c>
-      <c r="G141" s="71" t="s">
-        <v>417</v>
-      </c>
       <c r="H141" s="63" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I141" s="63"/>
       <c r="J141" s="63" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K141" s="63" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L141" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M141" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N141" s="63"/>
       <c r="O141" s="63" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="142" spans="1:15" ht="15.5">
@@ -12102,33 +12107,33 @@
       <c r="C142" s="56"/>
       <c r="D142" s="56"/>
       <c r="E142" s="71" t="s">
+        <v>415</v>
+      </c>
+      <c r="F142" s="71" t="s">
+        <v>421</v>
+      </c>
+      <c r="G142" s="71" t="s">
         <v>416</v>
       </c>
-      <c r="F142" s="71" t="s">
-        <v>422</v>
-      </c>
-      <c r="G142" s="71" t="s">
-        <v>417</v>
-      </c>
       <c r="H142" s="63" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I142" s="63"/>
       <c r="J142" s="63" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K142" s="63" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L142" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M142" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N142" s="63"/>
       <c r="O142" s="63" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="143" spans="1:15" ht="15.5">
@@ -12139,33 +12144,33 @@
       <c r="C143" s="56"/>
       <c r="D143" s="56"/>
       <c r="E143" s="71" t="s">
+        <v>415</v>
+      </c>
+      <c r="F143" s="71" t="s">
+        <v>422</v>
+      </c>
+      <c r="G143" s="71" t="s">
         <v>416</v>
       </c>
-      <c r="F143" s="71" t="s">
-        <v>423</v>
-      </c>
-      <c r="G143" s="71" t="s">
-        <v>417</v>
-      </c>
       <c r="H143" s="63" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I143" s="63"/>
       <c r="J143" s="63" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K143" s="63" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L143" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M143" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N143" s="63"/>
       <c r="O143" s="63" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="144" spans="1:15" ht="15.5">
@@ -12176,39 +12181,39 @@
       <c r="C144" s="56"/>
       <c r="D144" s="56"/>
       <c r="E144" s="71" t="s">
+        <v>415</v>
+      </c>
+      <c r="F144" s="71" t="s">
+        <v>424</v>
+      </c>
+      <c r="G144" s="71" t="s">
         <v>416</v>
       </c>
-      <c r="F144" s="71" t="s">
-        <v>425</v>
-      </c>
-      <c r="G144" s="71" t="s">
-        <v>417</v>
-      </c>
       <c r="H144" s="63" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I144" s="63"/>
       <c r="J144" s="63" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K144" s="63" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L144" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M144" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N144" s="63"/>
       <c r="O144" s="63" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="145" spans="1:15" ht="41.25" customHeight="1">
       <c r="A145" s="24"/>
-      <c r="B145" s="138" t="s">
-        <v>431</v>
+      <c r="B145" s="119" t="s">
+        <v>430</v>
       </c>
       <c r="C145" s="120"/>
       <c r="D145" s="120"/>
@@ -12228,7 +12233,7 @@
         <v>92</v>
       </c>
       <c r="B146" s="110" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C146" s="111"/>
       <c r="D146" s="111"/>
@@ -12236,30 +12241,30 @@
         <v>94</v>
       </c>
       <c r="F146" s="103" t="s">
+        <v>378</v>
+      </c>
+      <c r="G146" s="103" t="s">
         <v>379</v>
       </c>
-      <c r="G146" s="103" t="s">
+      <c r="H146" s="63" t="s">
         <v>380</v>
-      </c>
-      <c r="H146" s="63" t="s">
-        <v>381</v>
       </c>
       <c r="I146" s="63"/>
       <c r="J146" s="63" t="s">
+        <v>382</v>
+      </c>
+      <c r="K146" s="63" t="s">
         <v>383</v>
       </c>
-      <c r="K146" s="63" t="s">
-        <v>384</v>
-      </c>
       <c r="L146" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M146" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N146" s="63"/>
       <c r="O146" s="63" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
     </row>
     <row r="147" spans="1:15" ht="15.5">
@@ -12267,7 +12272,7 @@
         <v>92</v>
       </c>
       <c r="B147" s="110" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C147" s="111"/>
       <c r="D147" s="111"/>
@@ -12275,10 +12280,10 @@
         <v>94</v>
       </c>
       <c r="F147" s="103" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G147" s="103" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H147" s="63" t="s">
         <v>137</v>
@@ -12287,20 +12292,20 @@
         <v>83</v>
       </c>
       <c r="J147" s="63" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K147" s="63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L147" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M147" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N147" s="63"/>
       <c r="O147" s="63" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
     </row>
     <row r="148" spans="1:15" ht="15.5">
@@ -12314,35 +12319,35 @@
         <v>94</v>
       </c>
       <c r="F148" s="103" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G148" s="103" t="s">
+        <v>379</v>
+      </c>
+      <c r="H148" s="63" t="s">
         <v>380</v>
-      </c>
-      <c r="H148" s="63" t="s">
-        <v>381</v>
       </c>
       <c r="I148" s="63"/>
       <c r="J148" s="63" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K148" s="63" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L148" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M148" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N148" s="63"/>
       <c r="O148" s="63" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
     </row>
     <row r="149" spans="1:15" ht="15.5">
       <c r="A149" s="24" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B149" s="112"/>
       <c r="C149" s="112"/>
@@ -12351,10 +12356,10 @@
         <v>94</v>
       </c>
       <c r="F149" s="113" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G149" s="113" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H149" s="63" t="s">
         <v>82</v>
@@ -12363,28 +12368,28 @@
         <v>83</v>
       </c>
       <c r="J149" s="63" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K149" s="63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L149" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M149" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N149" s="63"/>
       <c r="O149" s="63" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
     </row>
     <row r="150" spans="1:15" ht="15.5">
       <c r="A150" s="24" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B150" s="112" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C150" s="112" t="s">
         <v>17</v>
@@ -12394,10 +12399,10 @@
         <v>94</v>
       </c>
       <c r="F150" s="113" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G150" s="113" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H150" s="63" t="s">
         <v>128</v>
@@ -12406,20 +12411,20 @@
         <v>83</v>
       </c>
       <c r="J150" s="63" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K150" s="63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L150" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M150" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N150" s="63"/>
       <c r="O150" s="63" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
     </row>
     <row r="151" spans="1:15" ht="15.5">
@@ -12430,52 +12435,52 @@
       <c r="C151" s="111"/>
       <c r="D151" s="111"/>
       <c r="E151" s="103" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F151" s="103" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G151" s="103" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H151" s="63" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I151" s="63"/>
       <c r="J151" s="63" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K151" s="63" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L151" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M151" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N151" s="63"/>
       <c r="O151" s="63" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
     </row>
     <row r="152" spans="1:15" ht="15.5">
       <c r="A152" s="24" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B152" s="112" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C152" s="112"/>
       <c r="D152" s="112"/>
       <c r="E152" s="113" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F152" s="113" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G152" s="113" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H152" s="63" t="s">
         <v>137</v>
@@ -12484,20 +12489,20 @@
         <v>83</v>
       </c>
       <c r="J152" s="63" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K152" s="63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L152" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M152" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N152" s="63"/>
       <c r="O152" s="63" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
     </row>
     <row r="153" spans="1:15" ht="15.5">
@@ -12508,52 +12513,52 @@
       <c r="C153" s="111"/>
       <c r="D153" s="111"/>
       <c r="E153" s="103" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F153" s="103" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G153" s="103" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H153" s="63" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I153" s="63"/>
       <c r="J153" s="63" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="K153" s="63" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L153" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M153" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N153" s="63"/>
       <c r="O153" s="63" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
     </row>
     <row r="154" spans="1:15" ht="15.5">
       <c r="A154" s="24" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B154" s="114" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C154" s="112"/>
       <c r="D154" s="112"/>
       <c r="E154" s="113" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F154" s="113" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G154" s="113" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H154" s="63" t="s">
         <v>82</v>
@@ -12562,20 +12567,20 @@
         <v>83</v>
       </c>
       <c r="J154" s="63" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="K154" s="63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L154" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M154" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N154" s="63"/>
       <c r="O154" s="63" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
     </row>
     <row r="155" spans="1:15" ht="15.5">
@@ -12583,40 +12588,40 @@
         <v>92</v>
       </c>
       <c r="B155" s="111" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C155" s="111" t="s">
         <v>17</v>
       </c>
       <c r="D155" s="111"/>
       <c r="E155" s="103" t="s">
+        <v>415</v>
+      </c>
+      <c r="F155" s="103" t="s">
+        <v>378</v>
+      </c>
+      <c r="G155" s="103" t="s">
         <v>416</v>
       </c>
-      <c r="F155" s="103" t="s">
-        <v>379</v>
-      </c>
-      <c r="G155" s="103" t="s">
-        <v>417</v>
-      </c>
       <c r="H155" s="63" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I155" s="63"/>
       <c r="J155" s="63" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K155" s="63" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L155" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M155" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N155" s="63"/>
       <c r="O155" s="63" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
     </row>
     <row r="156" spans="1:15" ht="15.5">
@@ -12624,40 +12629,40 @@
         <v>92</v>
       </c>
       <c r="B156" s="111" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C156" s="111" t="s">
         <v>17</v>
       </c>
       <c r="D156" s="111"/>
       <c r="E156" s="103" t="s">
+        <v>415</v>
+      </c>
+      <c r="F156" s="103" t="s">
+        <v>388</v>
+      </c>
+      <c r="G156" s="103" t="s">
         <v>416</v>
       </c>
-      <c r="F156" s="103" t="s">
-        <v>389</v>
-      </c>
-      <c r="G156" s="103" t="s">
-        <v>417</v>
-      </c>
       <c r="H156" s="63" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I156" s="63"/>
       <c r="J156" s="63" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K156" s="63" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L156" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M156" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N156" s="63"/>
       <c r="O156" s="63" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
     </row>
     <row r="157" spans="1:15" ht="15.5">
@@ -12665,38 +12670,38 @@
         <v>92</v>
       </c>
       <c r="B157" s="111" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C157" s="111"/>
       <c r="D157" s="102"/>
       <c r="E157" s="103" t="s">
+        <v>415</v>
+      </c>
+      <c r="F157" s="103" t="s">
+        <v>393</v>
+      </c>
+      <c r="G157" s="103" t="s">
         <v>416</v>
       </c>
-      <c r="F157" s="103" t="s">
-        <v>394</v>
-      </c>
-      <c r="G157" s="103" t="s">
-        <v>417</v>
-      </c>
       <c r="H157" s="63" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I157" s="63"/>
       <c r="J157" s="63" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K157" s="63" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L157" s="63" t="s">
         <v>72</v>
       </c>
       <c r="M157" s="63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N157" s="63"/>
       <c r="O157" s="63" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -12743,7 +12748,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1">
       <c r="A1" s="148"/>
-      <c r="B1" s="129"/>
+      <c r="B1" s="127"/>
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -13208,21 +13213,21 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.5">
       <c r="A1" s="116" t="s">
+        <v>433</v>
+      </c>
+      <c r="B1" s="116" t="s">
         <v>434</v>
       </c>
-      <c r="B1" s="116" t="s">
+      <c r="C1" s="116" t="s">
         <v>435</v>
-      </c>
-      <c r="C1" s="116" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.5">
       <c r="A2" s="115" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B2" s="117" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C2" s="117">
         <v>3</v>
@@ -13230,10 +13235,10 @@
     </row>
     <row r="3" spans="1:3" ht="15.5">
       <c r="A3" s="115" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B3" s="117" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C3" s="117">
         <v>1</v>
@@ -13241,10 +13246,10 @@
     </row>
     <row r="4" spans="1:3" ht="15.5">
       <c r="A4" s="115" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B4" s="117" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C4" s="117">
         <v>2</v>
@@ -13255,7 +13260,7 @@
         <v>156</v>
       </c>
       <c r="B5" s="117" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C5" s="117">
         <v>1</v>
@@ -13263,10 +13268,10 @@
     </row>
     <row r="6" spans="1:3" ht="15.5">
       <c r="A6" s="115" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B6" s="117" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C6" s="117">
         <v>2</v>
@@ -13277,7 +13282,7 @@
         <v>20</v>
       </c>
       <c r="B7" s="117" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C7" s="117">
         <v>1</v>
@@ -13285,10 +13290,10 @@
     </row>
     <row r="8" spans="1:3" ht="15.5">
       <c r="A8" s="115" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B8" s="117" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C8" s="117">
         <v>1</v>
@@ -13296,10 +13301,10 @@
     </row>
     <row r="9" spans="1:3" ht="15.5">
       <c r="A9" s="115" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B9" s="117" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C9" s="117">
         <v>1</v>
@@ -13307,10 +13312,10 @@
     </row>
     <row r="10" spans="1:3" ht="15.5">
       <c r="A10" s="115" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B10" s="117" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C10" s="117">
         <v>1</v>
@@ -13321,7 +13326,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="117" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C11" s="117">
         <v>2</v>
@@ -13332,7 +13337,7 @@
         <v>17</v>
       </c>
       <c r="B12" s="117" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C12" s="117">
         <v>2</v>
@@ -13343,7 +13348,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="117" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C13" s="117">
         <v>4</v>
@@ -13351,10 +13356,10 @@
     </row>
     <row r="14" spans="1:3" ht="15.5">
       <c r="A14" s="115" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B14" s="117" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C14" s="117">
         <v>1</v>
@@ -13362,10 +13367,10 @@
     </row>
     <row r="15" spans="1:3" ht="15.5">
       <c r="A15" s="115" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B15" s="117" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C15" s="117">
         <v>1</v>
@@ -13376,7 +13381,7 @@
         <v>31</v>
       </c>
       <c r="B16" s="117" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C16" s="117">
         <v>1</v>
@@ -13384,10 +13389,10 @@
     </row>
     <row r="17" spans="1:3" ht="15.5">
       <c r="A17" s="115" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B17" s="117" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C17" s="117">
         <v>4</v>
@@ -13395,10 +13400,10 @@
     </row>
     <row r="18" spans="1:3" ht="15.5">
       <c r="A18" s="115" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B18" s="117" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C18" s="117">
         <v>2</v>
@@ -13409,7 +13414,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="117" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C19" s="117">
         <v>3</v>
@@ -13417,10 +13422,10 @@
     </row>
     <row r="20" spans="1:3" ht="15.5">
       <c r="A20" s="115" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B20" s="117" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C20" s="117">
         <v>2</v>
@@ -13428,10 +13433,10 @@
     </row>
     <row r="21" spans="1:3" ht="15.5">
       <c r="A21" s="115" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B21" s="117" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C21" s="117">
         <v>1</v>
@@ -13439,10 +13444,10 @@
     </row>
     <row r="22" spans="1:3" ht="15.5">
       <c r="A22" s="115" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B22" s="117" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C22" s="117">
         <v>1</v>
@@ -13450,10 +13455,10 @@
     </row>
     <row r="23" spans="1:3" ht="15.5">
       <c r="A23" s="115" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B23" s="117" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C23" s="117">
         <v>1</v>
@@ -13464,7 +13469,7 @@
         <v>33</v>
       </c>
       <c r="B24" s="117" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C24" s="117">
         <v>3</v>
@@ -13472,10 +13477,10 @@
     </row>
     <row r="25" spans="1:3" ht="15.5">
       <c r="A25" s="115" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B25" s="117" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C25" s="117">
         <v>1</v>
@@ -13486,7 +13491,7 @@
         <v>109</v>
       </c>
       <c r="B26" s="117" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C26" s="117">
         <v>2</v>
@@ -13497,7 +13502,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="117" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C27" s="117">
         <v>1</v>
@@ -13508,7 +13513,7 @@
         <v>6</v>
       </c>
       <c r="B28" s="117" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C28" s="117">
         <v>2</v>
@@ -13519,7 +13524,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="117" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C29" s="117">
         <v>2</v>
@@ -13527,10 +13532,10 @@
     </row>
     <row r="30" spans="1:3" ht="15.5">
       <c r="A30" s="115" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B30" s="117" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C30" s="117">
         <v>1</v>
@@ -13538,10 +13543,10 @@
     </row>
     <row r="31" spans="1:3" ht="15.5">
       <c r="A31" s="115" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B31" s="117" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C31" s="117">
         <v>1</v>
@@ -13549,10 +13554,10 @@
     </row>
     <row r="32" spans="1:3" ht="15.5">
       <c r="A32" s="115" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B32" s="117" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C32" s="117">
         <v>1</v>
@@ -13560,10 +13565,10 @@
     </row>
     <row r="33" spans="1:3" ht="15.5">
       <c r="A33" s="115" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B33" s="117" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C33" s="117">
         <v>1</v>
@@ -13574,7 +13579,7 @@
         <v>91</v>
       </c>
       <c r="B34" s="117" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C34" s="117">
         <v>2</v>
@@ -13585,7 +13590,7 @@
         <v>146</v>
       </c>
       <c r="B35" s="117" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C35" s="117">
         <v>1</v>
@@ -13593,10 +13598,10 @@
     </row>
     <row r="36" spans="1:3" ht="15.5">
       <c r="A36" s="115" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B36" s="117" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C36" s="117">
         <v>2</v>
@@ -13607,7 +13612,7 @@
         <v>159</v>
       </c>
       <c r="B37" s="117" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C37" s="117">
         <v>1</v>
@@ -13615,10 +13620,10 @@
     </row>
     <row r="38" spans="1:3" ht="15.5">
       <c r="A38" s="115" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B38" s="117" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C38" s="117">
         <v>2</v>
@@ -13626,10 +13631,10 @@
     </row>
     <row r="39" spans="1:3" ht="15.5">
       <c r="A39" s="118" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B39" s="117" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C39" s="117">
         <v>1</v>
@@ -13640,7 +13645,7 @@
         <v>9</v>
       </c>
       <c r="B40" s="117" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C40" s="117">
         <v>2</v>
@@ -13648,10 +13653,10 @@
     </row>
     <row r="41" spans="1:3" ht="15.5">
       <c r="A41" s="115" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B41" s="117" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C41" s="117">
         <v>1</v>
